--- a/dcronchain/analysis/dcr_mining_hardware.xlsx
+++ b/dcronchain/analysis/dcr_mining_hardware.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code_development\checkonchain\checkonchain\dcronchain\analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AB77853-DEEC-4699-8FC9-070076F03A34}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8561713B-F771-4747-AA87-1B169D9F2827}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{C1DBD89A-FCF4-46FB-BE1F-46D52357B53B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{C1DBD89A-FCF4-46FB-BE1F-46D52357B53B}"/>
   </bookViews>
   <sheets>
     <sheet name="dcr_gpu" sheetId="4" r:id="rId1"/>
@@ -20,9 +20,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">btc_asics!$B$2:$K$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">dcr_asic_csv!$A$1:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">dcr_asic_csv!$A$1:$H$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">dcr_asics!$A$3:$M$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">dcr_gpu!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">dcr_gpu!$A$1:$K$1</definedName>
     <definedName name="result2097" localSheetId="0">dcr_gpu!#REF!</definedName>
     <definedName name="result2101" localSheetId="0">dcr_gpu!#REF!</definedName>
     <definedName name="result2103" localSheetId="0">dcr_gpu!#REF!</definedName>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="520">
   <si>
     <t>Model</t>
   </si>
@@ -4558,6 +4558,9 @@
   </si>
   <si>
     <t>gpu</t>
+  </si>
+  <si>
+    <t>blk_start</t>
   </si>
 </sst>
 </file>
@@ -4566,10 +4569,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4660,12 +4663,6 @@
     <font>
       <sz val="8"/>
       <color rgb="FF888888"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF333333"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -4916,7 +4913,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -4944,7 +4941,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4985,81 +4982,85 @@
     </xf>
     <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -5213,7 +5214,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9AC9FFF5-D711-4246-A753-1B1E7140E3CE}" type="CELLRANGE">
+                    <a:fld id="{E0F7E93A-D197-4FB6-B161-F6D2A818B092}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5232,7 +5233,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -5247,8 +5247,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{982E11C1-F5F7-4874-A50E-D08EBD6B7073}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{B14CF7C4-5BC0-42FC-87C2-E17B26F8E43D}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -5281,8 +5281,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E67CA91F-DD27-404C-8D43-249465B4BF5A}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{D4E6760E-9C28-497B-BD13-866DDB7C60E4}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -5315,8 +5315,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D677BB77-4A60-4A97-A244-1648CE2B59D9}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{BF4EE5A7-CBEB-4A94-9CD0-30ABD76E4C47}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -5349,8 +5349,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DF56DAF8-95DB-4510-BE09-9D6CE8D5B5C3}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{04E19EA6-ACA8-49B1-8C3F-5F6EFFF0EA7B}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -5383,8 +5383,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{790EEFBD-2164-479B-817C-AA0C469F30C2}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{C8541356-9CAC-4DD8-8AD7-90983618AFA6}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -5417,8 +5417,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D85CD033-C012-4B5A-A90E-3660FD41F170}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{17E7BADA-3834-44E8-8E21-01A1763AFA1A}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -5451,8 +5451,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1EAC41F2-A912-4017-A814-294CFFE8CFEA}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{DDB25724-4423-466B-9BB9-CFAB22C050E6}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -5485,8 +5485,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{21D951BB-9260-4222-BA34-B1EB2E8BDC0A}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{78DC1B23-3D35-4B30-B0D4-2E416D10D912}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -5519,8 +5519,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4C0B58E7-F284-418E-8803-B2C2A4BBA670}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{E1EB8FEC-6250-4A03-9DCE-8965607BD63A}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -5553,8 +5553,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1CE1A748-E3AF-43CA-8A11-1E58AA9B48A5}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{68634EF1-D698-4236-BCEE-100D13916A8F}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -5587,8 +5587,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4E3C24C3-BE25-4E8F-B252-7FA3CA974014}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{1FA77284-4E0E-430E-B9DD-09C490626139}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -5621,8 +5621,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A62C38B9-AA15-40BB-90F6-FE12F3B1835C}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{65F34B8F-CF81-4C52-834C-4512C0CB2218}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -5655,8 +5655,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{998F6758-9CC3-49B2-AA8A-380747700FE3}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{EFE1ABD3-AF9B-479A-B98F-B30ABC31ECBF}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -5689,8 +5689,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8B7D4C1D-8418-4176-8A15-B7EA10288BAA}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{1A6B2DB9-0917-4026-BD6C-E7375EDE124C}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -5723,8 +5723,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8EE88A3B-49C6-4889-8E71-6AC26B00AC8F}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{47C0F055-8073-424A-98E7-BCD9A91C08B2}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -5757,8 +5757,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C9C9DDD6-E316-4A30-B406-A2525603C167}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{F5175597-FF10-4089-8060-5CBED9297654}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6070,7 +6070,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5358804E-A2F2-44D2-941E-CBC3881DB8DC}" type="CELLRANGE">
+                    <a:fld id="{78D8BA5A-1EE8-4B87-80A2-7221A6FC85AC}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6089,7 +6089,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -6104,8 +6103,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3081D2DF-7E32-46E1-B90F-B331CC8A53F1}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{50A9B696-6A68-4736-8BD3-4143DD4BEE64}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6138,8 +6137,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{64677C2A-3899-41C2-B704-1FD0CA94B324}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{598F9572-9DEE-4C0B-A443-E5D1BA1CA4FE}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6172,8 +6171,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4B6B9A0E-C9B2-438C-9A66-D4CC94CBBF25}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{F220AE27-AB99-4929-B2BE-2A4C2580CF2C}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6206,8 +6205,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F19CE083-F2E5-4164-910C-0E3C3E6D968B}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{3D6B3DF6-67B2-4DB2-9CFD-8935E95A1ED4}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6240,8 +6239,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D0ED54E9-4DA4-491B-8F4E-745F52D37CBF}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{69F9FDF5-16D5-43CD-9618-F8FFF9410BAA}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6274,8 +6273,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{932E5959-6934-4A0D-B1B7-AA37C4F00B60}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{A7BD81F7-308F-4034-9AEF-6925C7D36BD3}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6308,8 +6307,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B5CD26A5-0DE2-4BDC-B74C-2EE8DA6E562C}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{CDB07923-FC16-4700-8FD3-A1DEC7B7E2C2}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6342,8 +6341,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8B2583BB-B8B8-47B8-BA18-0FE5F98A2AE3}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{9FCA25F1-925E-4D20-8F77-1008F7595AB1}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6376,8 +6375,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D83C7855-49A2-4CA1-8512-2B952726C8A4}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{2459810A-50B8-4482-82AF-D19C574960E3}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6410,8 +6409,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2E2130E8-8C7A-48E1-AD72-156CEA0960E7}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{09A62969-72B4-4CA9-8D54-DFAADB6E0697}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6444,8 +6443,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D5839D55-81ED-45E0-805D-ED4A098FC34E}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{E59CBF1E-BA5E-4C27-A6C2-35C3A1AA16A3}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6478,8 +6477,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{675AD6C2-0047-42BA-8F56-658B60535E20}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{D9C19468-556C-4561-8560-3CF3B9677643}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6512,8 +6511,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DD1C38FB-532D-475C-8C76-8141E1315885}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{E23641D3-336E-403C-8EA1-4DFC9253F1C7}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6546,8 +6545,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DA55915D-9EE9-462A-B703-1AC1DA4210C1}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{074F2BA0-4888-43C2-B651-03761DA404C5}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6580,8 +6579,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B5850BD5-1DC8-4ADD-BDFA-40663D7AB602}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{49482295-EDB7-4999-8676-2B35520FAF70}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6614,8 +6613,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{219CD0EB-6DED-47D4-8695-BDD57901BEF3}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{1A7D1734-DD8C-4975-B7D1-04BF381B010D}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -7976,7 +7975,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A5518272-ECBA-406A-BCFF-B2E1D5C89BEB}" type="CELLRANGE">
+                    <a:fld id="{8D30309C-9EA5-424C-A289-23063C9D0ED6}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -8009,7 +8008,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1B27512E-6CB4-4AD5-B9D2-9AF04EA5B417}" type="CELLRANGE">
+                    <a:fld id="{31D87B03-30F3-4C28-93F3-DEF33BF73071}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -8042,7 +8041,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C3077620-8F01-407E-A041-23998AC3A6A5}" type="CELLRANGE">
+                    <a:fld id="{C52BBF30-85C0-4A1F-913D-6CE409679FB1}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -8075,7 +8074,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{789F6E85-E1FC-4DAC-8139-E60F11CAFCA6}" type="CELLRANGE">
+                    <a:fld id="{3F5F5C5C-9572-402E-8591-9DFB2F3E67C7}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -8108,7 +8107,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5F745EA2-4436-4907-A857-702A48BFB5F0}" type="CELLRANGE">
+                    <a:fld id="{CE7241BB-BD79-4557-9EB4-A6579D3907B2}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -8141,7 +8140,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{51FB6698-DD99-4258-8014-8FA7BA53DEFD}" type="CELLRANGE">
+                    <a:fld id="{40731534-EF04-4106-B80E-071A1A1FD937}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -8174,7 +8173,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{017EAB6E-3941-4580-B12F-12D032644099}" type="CELLRANGE">
+                    <a:fld id="{9C1A2C9E-4412-496E-983D-AE66BB82B64F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -8207,7 +8206,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{82A54158-4B19-477B-AF46-1C48DE49A4DE}" type="CELLRANGE">
+                    <a:fld id="{95E566B9-1267-48CA-A661-7CBA603A4B43}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -8240,7 +8239,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C53C5CBA-DA12-44DB-8FA2-C49C1A4C1C60}" type="CELLRANGE">
+                    <a:fld id="{3CAAEF18-452F-4742-AEEA-9802C999D633}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -8273,7 +8272,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{440B9D54-8497-4B9D-BE0B-9D42CCA5E6C5}" type="CELLRANGE">
+                    <a:fld id="{0BFD99C8-5465-4613-B22F-E381629F67A3}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -8306,7 +8305,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CF51505C-13F0-4E9D-95D4-CA51BFDD918B}" type="CELLRANGE">
+                    <a:fld id="{5E76FD88-FBA4-4C87-93B5-BDC04A409EC9}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -8339,7 +8338,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1F17F494-59DE-491C-ACD8-27F3B852246D}" type="CELLRANGE">
+                    <a:fld id="{64F7D7A0-AAAB-4E19-96F6-5D17C0D237DC}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -8372,7 +8371,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{41FDDFA8-A0A8-491D-BAF3-26D20A6E3154}" type="CELLRANGE">
+                    <a:fld id="{61EC12B1-C7D4-4B74-8A50-51CE9FEF6094}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -8405,7 +8404,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4EBAB9A9-EE90-4F34-BAF4-D05C2444B05A}" type="CELLRANGE">
+                    <a:fld id="{B2129E50-F96A-4CF2-8A02-1CDCA808F587}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -8438,7 +8437,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{ED1C9FB7-4A07-4F42-9DEE-39B5EEDAA54D}" type="CELLRANGE">
+                    <a:fld id="{376BCD0C-121D-45EB-AE4C-59D38B787BBB}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -8471,7 +8470,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{748D4C15-5100-4FAD-ADB6-652975BB744B}" type="CELLRANGE">
+                    <a:fld id="{BDE1C47C-D0A7-48DF-8B49-60633808BFDB}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -8504,7 +8503,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6531F546-D802-48AD-9A7C-95A1C3AE2514}" type="CELLRANGE">
+                    <a:fld id="{B155B443-A0BB-4FF8-9ABE-4CC06DE3F67A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -9067,7 +9066,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{24B9F0E5-A1C8-4D1F-9394-750FBE819B2B}" type="CELLRANGE">
+                    <a:fld id="{A1078B49-F768-4A5C-929A-214C7B9E56AE}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -9086,7 +9085,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -9114,7 +9112,7 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000002-65BE-4EF4-8BE1-06EFF9C471AB}"/>
@@ -9128,8 +9126,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4723E65D-2F5B-47F4-89B0-998863364488}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{C86EFFF7-9AA8-44FE-98DD-A1A1154B6D03}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -9162,8 +9160,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8CAC314E-B68D-45FA-8B43-69C31916B543}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{B8BB7E7A-9315-4CC2-A7E9-3C921C43999C}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -9196,8 +9194,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4BB3850E-A3BD-405D-A012-9141E222852C}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{EB450248-9473-41A3-B17A-37141DEEFF7B}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -9230,8 +9228,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3A2AD3D3-31E7-4516-9577-62AAE2849679}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{E6B34562-64ED-4272-ACB5-18371051EF82}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -9277,7 +9275,7 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000007-65BE-4EF4-8BE1-06EFF9C471AB}"/>
@@ -9304,7 +9302,7 @@
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="0"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000008-65BE-4EF4-8BE1-06EFF9C471AB}"/>
@@ -9318,8 +9316,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A0313773-6275-433E-92E0-669E84DB8721}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{0FE51C3D-913B-4BC7-BFC8-FBDD8B0F7A8F}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -9352,8 +9350,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6704D004-7DE6-493E-8A0D-F74674B3BAFE}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{2A05BA36-98B7-4C54-92B7-77970003D4F6}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -9386,8 +9384,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1ED24674-1B3B-4928-A892-07726C9FEDB4}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{F033827C-D8BA-4187-BE7F-BB63E7CD07A0}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -9420,8 +9418,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1D4757AD-22D3-495F-A1CC-B27BD5ED2B4D}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{B331FF88-9A27-48ED-AFE4-7762BF12CF9C}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -9454,8 +9452,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{623300E8-B89C-4915-B090-E204CA0B58E0}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{493E7013-53EF-4B61-A0ED-CA1C5D9C211F}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -9488,8 +9486,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6852A3C6-C6DD-4F55-8FB5-83C7620A07BC}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{D48754B5-0DCC-44AB-A987-2750C22019F0}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -9522,8 +9520,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9E8EF66B-2E3F-484F-9248-810A992E07B3}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{0A90BD33-60A9-4D19-9F1B-5623D116C0E8}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -9556,8 +9554,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C48CD5B7-6A0F-432E-AF41-009409E25860}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{B0155440-CE82-4C75-A0C8-BCA894C46449}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -9590,8 +9588,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0F37BE04-BD46-4DA6-982B-5019490E7334}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{D51FA4A8-C710-45CA-8FE5-49C6F8D150F8}" type="CELLRANGE">
+                      <a:rPr lang="en-AU"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -13116,18 +13114,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3ADB9C9-81AE-4048-9C1B-5740FE3FCBBB}">
   <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" style="13" customWidth="1"/>
-    <col min="2" max="2" width="25.28515625" style="13" customWidth="1"/>
+    <col min="1" max="1" width="5.44140625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" style="13" customWidth="1"/>
     <col min="3" max="3" width="9" style="13" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" style="13" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" style="13" customWidth="1"/>
     <col min="5" max="5" width="14" style="13" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" style="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="28" t="s">
         <v>446</v>
       </c>
@@ -13162,468 +13161,468 @@
         <v>515</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="33">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="C2" s="33">
-        <v>0.39</v>
+        <v>1.01</v>
       </c>
       <c r="D2" s="33">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>482</v>
-      </c>
-      <c r="G2">
+        <v>468</v>
+      </c>
+      <c r="G2" s="42">
         <f>C2/1000</f>
-        <v>3.8999999999999999E-4</v>
-      </c>
-      <c r="H2">
+        <v>1.01E-3</v>
+      </c>
+      <c r="H2" s="42">
         <f>LEFT(F2,LEN(F2)-2)/1000</f>
-        <v>0.16</v>
-      </c>
-      <c r="I2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I2" s="42">
         <f>LEFT(E2,LEN(E2)-4)+0</f>
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="J2" s="38">
         <f>G2*60^2/H2</f>
-        <v>8.7749999999999986</v>
+        <v>51.942857142857143</v>
       </c>
       <c r="K2" s="55">
         <f>J2/I2</f>
-        <v>0.1070121951219512</v>
+        <v>0.30375939849624062</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="30">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C3" s="30">
-        <v>0.78</v>
+        <v>0.85</v>
       </c>
       <c r="D3" s="30">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F3" s="30" t="s">
-        <v>466</v>
-      </c>
-      <c r="G3">
+        <v>474</v>
+      </c>
+      <c r="G3" s="42">
         <f>C3/1000</f>
-        <v>7.7999999999999999E-4</v>
-      </c>
-      <c r="H3">
+        <v>8.4999999999999995E-4</v>
+      </c>
+      <c r="H3" s="42">
         <f>LEFT(F3,LEN(F3)-2)/1000</f>
-        <v>0.2</v>
-      </c>
-      <c r="I3">
+        <v>0.06</v>
+      </c>
+      <c r="I3" s="42">
         <f>LEFT(E3,LEN(E3)-4)+0</f>
-        <v>391</v>
+        <v>170</v>
       </c>
       <c r="J3" s="38">
-        <f t="shared" ref="J3:J23" si="0">G3*60^2/H3</f>
-        <v>14.04</v>
+        <f>G3*60^2/H3</f>
+        <v>50.999999999999993</v>
       </c>
       <c r="K3" s="55">
-        <f t="shared" ref="K3:K23" si="1">J3/I3</f>
-        <v>3.5907928388746804E-2</v>
+        <f>J3/I3</f>
+        <v>0.29999999999999993</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="32">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="C4" s="32">
-        <v>0.63</v>
+        <v>0.92</v>
       </c>
       <c r="D4" s="32">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>466</v>
-      </c>
-      <c r="G4">
+        <v>471</v>
+      </c>
+      <c r="G4" s="42">
         <f>C4/1000</f>
-        <v>6.3000000000000003E-4</v>
-      </c>
-      <c r="H4">
+        <v>9.2000000000000003E-4</v>
+      </c>
+      <c r="H4" s="42">
         <f>LEFT(F4,LEN(F4)-2)/1000</f>
-        <v>0.2</v>
-      </c>
-      <c r="I4">
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="42">
         <f>LEFT(E4,LEN(E4)-4)+0</f>
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="J4" s="38">
-        <f t="shared" si="0"/>
-        <v>11.34</v>
+        <f>G4*60^2/H4</f>
+        <v>33.119999999999997</v>
       </c>
       <c r="K4" s="55">
-        <f t="shared" si="1"/>
-        <v>7.7142857142857138E-2</v>
+        <f>J4/I4</f>
+        <v>0.29309734513274333</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="33">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="C5" s="33">
-        <v>0.26</v>
+        <v>2.83</v>
       </c>
       <c r="D5" s="33">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>485</v>
+        <v>457</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>486</v>
-      </c>
-      <c r="G5">
+        <v>458</v>
+      </c>
+      <c r="G5" s="42">
         <f>C5/1000</f>
-        <v>2.6000000000000003E-4</v>
-      </c>
-      <c r="H5">
+        <v>2.8300000000000001E-3</v>
+      </c>
+      <c r="H5" s="42">
         <f>LEFT(F5,LEN(F5)-2)/1000</f>
-        <v>0.11</v>
-      </c>
-      <c r="I5">
+        <v>0.15</v>
+      </c>
+      <c r="I5" s="42">
         <f>LEFT(E5,LEN(E5)-4)+0</f>
-        <v>184</v>
+        <v>246</v>
       </c>
       <c r="J5" s="38">
-        <f t="shared" si="0"/>
-        <v>8.5090909090909097</v>
+        <f>G5*60^2/H5</f>
+        <v>67.92</v>
       </c>
       <c r="K5" s="55">
-        <f t="shared" si="1"/>
-        <v>4.6245059288537553E-2</v>
+        <f>J5/I5</f>
+        <v>0.27609756097560978</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="30">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="C6" s="30">
-        <v>1.07</v>
+        <v>0.51</v>
       </c>
       <c r="D6" s="30">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="E6" s="30" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>466</v>
-      </c>
-      <c r="G6">
+        <v>480</v>
+      </c>
+      <c r="G6" s="42">
         <f>C6/1000</f>
-        <v>1.07E-3</v>
-      </c>
-      <c r="H6">
+        <v>5.1000000000000004E-4</v>
+      </c>
+      <c r="H6" s="42">
         <f>LEFT(F6,LEN(F6)-2)/1000</f>
-        <v>0.2</v>
-      </c>
-      <c r="I6">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="I6" s="42">
         <f>LEFT(E6,LEN(E6)-4)+0</f>
-        <v>609</v>
+        <v>155</v>
       </c>
       <c r="J6" s="38">
-        <f t="shared" si="0"/>
-        <v>19.259999999999998</v>
+        <f>G6*60^2/H6</f>
+        <v>24.48</v>
       </c>
       <c r="K6" s="55">
-        <f t="shared" si="1"/>
-        <v>3.1625615763546798E-2</v>
+        <f>J6/I6</f>
+        <v>0.15793548387096776</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="32">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C7" s="32">
-        <v>1.07</v>
+        <v>1.74</v>
       </c>
       <c r="D7" s="32">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="G7">
         <f>C7/1000</f>
-        <v>1.07E-3</v>
+        <v>1.74E-3</v>
       </c>
       <c r="H7">
         <f>LEFT(F7,LEN(F7)-2)/1000</f>
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
       <c r="I7">
         <f>LEFT(E7,LEN(E7)-4)+0</f>
-        <v>611</v>
+        <v>223</v>
       </c>
       <c r="J7" s="38">
-        <f t="shared" si="0"/>
-        <v>11.005714285714285</v>
+        <f>G7*60^2/H7</f>
+        <v>28.472727272727273</v>
       </c>
       <c r="K7" s="55">
-        <f t="shared" si="1"/>
-        <v>1.801262567220014E-2</v>
+        <f>J7/I7</f>
+        <v>0.12768039135752141</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="33">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="C8" s="33">
-        <v>1.74</v>
+        <v>0.39</v>
       </c>
       <c r="D8" s="33">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>460</v>
+        <v>481</v>
       </c>
       <c r="F8" s="36" t="s">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="G8">
         <f>C8/1000</f>
-        <v>1.74E-3</v>
+        <v>3.8999999999999999E-4</v>
       </c>
       <c r="H8">
         <f>LEFT(F8,LEN(F8)-2)/1000</f>
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="I8">
         <f>LEFT(E8,LEN(E8)-4)+0</f>
-        <v>223</v>
+        <v>82</v>
       </c>
       <c r="J8" s="38">
-        <f t="shared" si="0"/>
-        <v>28.472727272727273</v>
+        <f>G8*60^2/H8</f>
+        <v>8.7749999999999986</v>
       </c>
       <c r="K8" s="55">
-        <f t="shared" si="1"/>
-        <v>0.12768039135752141</v>
+        <f>J8/I8</f>
+        <v>0.1070121951219512</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="30">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="C9" s="30">
-        <v>1.51</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="D9" s="30">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>458</v>
-      </c>
-      <c r="G9">
+        <v>484</v>
+      </c>
+      <c r="G9" s="42">
         <f>C9/1000</f>
-        <v>1.5100000000000001E-3</v>
-      </c>
-      <c r="H9">
+        <v>2.9E-4</v>
+      </c>
+      <c r="H9" s="42">
         <f>LEFT(F9,LEN(F9)-2)/1000</f>
-        <v>0.15</v>
-      </c>
-      <c r="I9">
+        <v>0.08</v>
+      </c>
+      <c r="I9" s="42">
         <f>LEFT(E9,LEN(E9)-4)+0</f>
-        <v>406</v>
+        <v>125</v>
       </c>
       <c r="J9" s="38">
-        <f t="shared" si="0"/>
-        <v>36.24</v>
+        <f>G9*60^2/H9</f>
+        <v>13.05</v>
       </c>
       <c r="K9" s="55">
-        <f t="shared" si="1"/>
-        <v>8.9261083743842368E-2</v>
+        <f>J9/I9</f>
+        <v>0.10440000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="33">
-        <v>19</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>505</v>
+        <v>3</v>
+      </c>
+      <c r="B10" s="60" t="s">
+        <v>489</v>
       </c>
       <c r="C10" s="33">
-        <v>0.51</v>
+        <v>3.09</v>
       </c>
       <c r="D10" s="33">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>479</v>
+        <v>455</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
       <c r="G10" s="42">
         <f>C10/1000</f>
-        <v>5.1000000000000004E-4</v>
+        <v>3.0899999999999999E-3</v>
       </c>
       <c r="H10" s="42">
         <f>LEFT(F10,LEN(F10)-2)/1000</f>
-        <v>7.4999999999999997E-2</v>
+        <v>0.18</v>
       </c>
       <c r="I10" s="42">
         <f>LEFT(E10,LEN(E10)-4)+0</f>
-        <v>155</v>
+        <v>619</v>
       </c>
       <c r="J10" s="38">
-        <f t="shared" si="0"/>
-        <v>24.48</v>
+        <f>G10*60^2/H10</f>
+        <v>61.8</v>
       </c>
       <c r="K10" s="55">
-        <f t="shared" si="1"/>
-        <v>0.15793548387096776</v>
+        <f>J10/I10</f>
+        <v>9.9838449111470107E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C11" s="33">
-        <v>2.4</v>
+        <v>1.51</v>
       </c>
       <c r="D11" s="33">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>453</v>
-      </c>
-      <c r="G11" s="42">
+        <v>458</v>
+      </c>
+      <c r="G11">
         <f>C11/1000</f>
-        <v>2.3999999999999998E-3</v>
-      </c>
-      <c r="H11" s="42">
+        <v>1.5100000000000001E-3</v>
+      </c>
+      <c r="H11">
         <f>LEFT(F11,LEN(F11)-2)/1000</f>
-        <v>0.25</v>
-      </c>
-      <c r="I11" s="42">
+        <v>0.15</v>
+      </c>
+      <c r="I11">
         <f>LEFT(E11,LEN(E11)-4)+0</f>
-        <v>605</v>
+        <v>406</v>
       </c>
       <c r="J11" s="38">
-        <f t="shared" si="0"/>
-        <v>34.559999999999995</v>
+        <f>G11*60^2/H11</f>
+        <v>36.24</v>
       </c>
       <c r="K11" s="55">
-        <f t="shared" si="1"/>
-        <v>5.7123966942148753E-2</v>
+        <f>J11/I11</f>
+        <v>8.9261083743842368E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="33">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C12" s="33">
-        <v>0.95</v>
+        <v>0.63</v>
       </c>
       <c r="D12" s="33">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="F12" s="33" t="s">
-        <v>454</v>
-      </c>
-      <c r="G12" s="42">
+        <v>466</v>
+      </c>
+      <c r="G12">
         <f>C12/1000</f>
-        <v>9.5E-4</v>
-      </c>
-      <c r="H12" s="42">
+        <v>6.3000000000000003E-4</v>
+      </c>
+      <c r="H12">
         <f>LEFT(F12,LEN(F12)-2)/1000</f>
-        <v>0.3</v>
-      </c>
-      <c r="I12" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="I12">
         <f>LEFT(E12,LEN(E12)-4)+0</f>
-        <v>520</v>
+        <v>147</v>
       </c>
       <c r="J12" s="38">
-        <f t="shared" si="0"/>
-        <v>11.4</v>
+        <f>G12*60^2/H12</f>
+        <v>11.34</v>
       </c>
       <c r="K12" s="55">
-        <f t="shared" si="1"/>
-        <v>2.1923076923076924E-2</v>
+        <f>J12/I12</f>
+        <v>7.7142857142857138E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="C13" s="33">
-        <v>0.92</v>
+        <v>0.52</v>
       </c>
       <c r="D13" s="33">
         <v>2015</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="F13" s="33" t="s">
         <v>471</v>
       </c>
       <c r="G13" s="42">
         <f>C13/1000</f>
-        <v>9.2000000000000003E-4</v>
+        <v>5.2000000000000006E-4</v>
       </c>
       <c r="H13" s="42">
         <f>LEFT(F13,LEN(F13)-2)/1000</f>
@@ -13631,39 +13630,39 @@
       </c>
       <c r="I13" s="42">
         <f>LEFT(E13,LEN(E13)-4)+0</f>
-        <v>113</v>
+        <v>273</v>
       </c>
       <c r="J13" s="38">
-        <f t="shared" si="0"/>
-        <v>33.119999999999997</v>
+        <f>G13*60^2/H13</f>
+        <v>18.720000000000002</v>
       </c>
       <c r="K13" s="55">
-        <f t="shared" si="1"/>
-        <v>0.29309734513274333</v>
+        <f>J13/I13</f>
+        <v>6.8571428571428575E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="33">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="C14" s="33">
-        <v>0.89</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D14" s="33">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>472</v>
+        <v>452</v>
       </c>
       <c r="F14" s="33" t="s">
         <v>453</v>
       </c>
       <c r="G14" s="42">
         <f>C14/1000</f>
-        <v>8.9000000000000006E-4</v>
+        <v>4.5999999999999999E-3</v>
       </c>
       <c r="H14" s="42">
         <f>LEFT(F14,LEN(F14)-2)/1000</f>
@@ -13671,388 +13670,393 @@
       </c>
       <c r="I14" s="42">
         <f>LEFT(E14,LEN(E14)-4)+0</f>
-        <v>445</v>
+        <v>1041</v>
       </c>
       <c r="J14" s="38">
-        <f t="shared" si="0"/>
-        <v>12.816000000000001</v>
+        <f>G14*60^2/H14</f>
+        <v>66.239999999999995</v>
       </c>
       <c r="K14" s="55">
-        <f t="shared" si="1"/>
-        <v>2.8800000000000003E-2</v>
+        <f>J14/I14</f>
+        <v>6.3631123919308349E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="C15" s="33">
-        <v>0.66</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="33">
         <v>2015</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="G15" s="42">
         <f>C15/1000</f>
-        <v>6.6E-4</v>
+        <v>2.3999999999999998E-3</v>
       </c>
       <c r="H15" s="42">
         <f>LEFT(F15,LEN(F15)-2)/1000</f>
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="I15" s="42">
         <f>LEFT(E15,LEN(E15)-4)+0</f>
-        <v>438</v>
+        <v>605</v>
       </c>
       <c r="J15" s="38">
-        <f t="shared" si="0"/>
-        <v>10.799999999999999</v>
+        <f>G15*60^2/H15</f>
+        <v>34.559999999999995</v>
       </c>
       <c r="K15" s="55">
-        <f t="shared" si="1"/>
-        <v>2.4657534246575338E-2</v>
+        <f>J15/I15</f>
+        <v>5.7123966942148753E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="33">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C16" s="33">
-        <v>0.52</v>
+        <v>0.26</v>
       </c>
       <c r="D16" s="33">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="F16" s="33" t="s">
-        <v>471</v>
-      </c>
-      <c r="G16" s="42">
+        <v>486</v>
+      </c>
+      <c r="G16">
         <f>C16/1000</f>
-        <v>5.2000000000000006E-4</v>
-      </c>
-      <c r="H16" s="42">
+        <v>2.6000000000000003E-4</v>
+      </c>
+      <c r="H16">
         <f>LEFT(F16,LEN(F16)-2)/1000</f>
-        <v>0.1</v>
-      </c>
-      <c r="I16" s="42">
+        <v>0.11</v>
+      </c>
+      <c r="I16">
         <f>LEFT(E16,LEN(E16)-4)+0</f>
-        <v>273</v>
+        <v>184</v>
       </c>
       <c r="J16" s="38">
-        <f t="shared" si="0"/>
-        <v>18.720000000000002</v>
+        <f>G16*60^2/H16</f>
+        <v>8.5090909090909097</v>
       </c>
       <c r="K16" s="55">
-        <f t="shared" si="1"/>
-        <v>6.8571428571428575E-2</v>
+        <f>J16/I16</f>
+        <v>4.6245059288537553E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="C17" s="33">
-        <v>0.28999999999999998</v>
+        <v>0.78</v>
       </c>
       <c r="D17" s="33">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>484</v>
-      </c>
-      <c r="G17" s="42">
+        <v>466</v>
+      </c>
+      <c r="G17">
         <f>C17/1000</f>
-        <v>2.9E-4</v>
-      </c>
-      <c r="H17" s="42">
+        <v>7.7999999999999999E-4</v>
+      </c>
+      <c r="H17">
         <f>LEFT(F17,LEN(F17)-2)/1000</f>
-        <v>0.08</v>
-      </c>
-      <c r="I17" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="I17">
         <f>LEFT(E17,LEN(E17)-4)+0</f>
-        <v>125</v>
+        <v>391</v>
       </c>
       <c r="J17" s="38">
-        <f t="shared" si="0"/>
-        <v>13.05</v>
+        <f>G17*60^2/H17</f>
+        <v>14.04</v>
       </c>
       <c r="K17" s="55">
-        <f t="shared" si="1"/>
-        <v>0.10440000000000001</v>
+        <f>J17/I17</f>
+        <v>3.5907928388746804E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="C18" s="40">
-        <v>3.43</v>
+        <v>1.07</v>
       </c>
       <c r="D18" s="40">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="E18" s="40" t="s">
-        <v>511</v>
+        <v>465</v>
       </c>
       <c r="F18" s="40" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="G18" s="41">
         <f>C18/1000</f>
-        <v>3.4300000000000003E-3</v>
+        <v>1.07E-3</v>
       </c>
       <c r="H18" s="41">
         <f>LEFT(F18,LEN(F18)-2)/1000</f>
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I18" s="41">
         <f>LEFT(E18,LEN(E18)-4)+0</f>
-        <v>2895</v>
+        <v>609</v>
       </c>
       <c r="J18" s="38">
-        <f t="shared" si="0"/>
-        <v>41.160000000000004</v>
+        <f>G18*60^2/H18</f>
+        <v>19.259999999999998</v>
       </c>
       <c r="K18" s="55">
-        <f t="shared" si="1"/>
-        <v>1.4217616580310882E-2</v>
+        <f>J18/I18</f>
+        <v>3.1625615763546798E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="47">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B19" s="35" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="C19" s="33">
-        <v>3.09</v>
+        <v>0.89</v>
       </c>
       <c r="D19" s="33">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>455</v>
+        <v>472</v>
       </c>
       <c r="F19" s="33" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="G19" s="42">
         <f>C19/1000</f>
-        <v>3.0899999999999999E-3</v>
+        <v>8.9000000000000006E-4</v>
       </c>
       <c r="H19" s="42">
         <f>LEFT(F19,LEN(F19)-2)/1000</f>
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="I19" s="42">
         <f>LEFT(E19,LEN(E19)-4)+0</f>
-        <v>619</v>
+        <v>445</v>
       </c>
       <c r="J19" s="38">
-        <f t="shared" si="0"/>
-        <v>61.8</v>
+        <f>G19*60^2/H19</f>
+        <v>12.816000000000001</v>
       </c>
       <c r="K19" s="55">
-        <f t="shared" si="1"/>
-        <v>9.9838449111470107E-2</v>
+        <f>J19/I19</f>
+        <v>2.8800000000000003E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="47">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="C20" s="33">
-        <v>2.83</v>
+        <v>0.66</v>
       </c>
       <c r="D20" s="33">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="F20" s="33" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G20" s="42">
         <f>C20/1000</f>
-        <v>2.8300000000000001E-3</v>
+        <v>6.6E-4</v>
       </c>
       <c r="H20" s="42">
         <f>LEFT(F20,LEN(F20)-2)/1000</f>
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="I20" s="42">
         <f>LEFT(E20,LEN(E20)-4)+0</f>
-        <v>246</v>
+        <v>438</v>
       </c>
       <c r="J20" s="38">
-        <f t="shared" si="0"/>
-        <v>67.92</v>
+        <f>G20*60^2/H20</f>
+        <v>10.799999999999999</v>
       </c>
       <c r="K20" s="55">
-        <f t="shared" si="1"/>
-        <v>0.27609756097560978</v>
+        <f>J20/I20</f>
+        <v>2.4657534246575338E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="47">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B21" s="35" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C21" s="33">
-        <v>1.01</v>
+        <v>0.95</v>
       </c>
       <c r="D21" s="33">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="E21" s="33" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F21" s="33" t="s">
-        <v>468</v>
+        <v>454</v>
       </c>
       <c r="G21" s="42">
         <f>C21/1000</f>
-        <v>1.01E-3</v>
+        <v>9.5E-4</v>
       </c>
       <c r="H21" s="42">
         <f>LEFT(F21,LEN(F21)-2)/1000</f>
-        <v>7.0000000000000007E-2</v>
+        <v>0.3</v>
       </c>
       <c r="I21" s="42">
         <f>LEFT(E21,LEN(E21)-4)+0</f>
-        <v>171</v>
+        <v>520</v>
       </c>
       <c r="J21" s="38">
-        <f t="shared" si="0"/>
-        <v>51.942857142857143</v>
+        <f>G21*60^2/H21</f>
+        <v>11.4</v>
       </c>
       <c r="K21" s="55">
-        <f t="shared" si="1"/>
-        <v>0.30375939849624062</v>
+        <f>J21/I21</f>
+        <v>2.1923076923076924E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="43">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="C22" s="44">
-        <v>0.85</v>
+        <v>1.07</v>
       </c>
       <c r="D22" s="44">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="F22" s="44" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="G22" s="45">
         <f>C22/1000</f>
-        <v>8.4999999999999995E-4</v>
+        <v>1.07E-3</v>
       </c>
       <c r="H22" s="45">
         <f>LEFT(F22,LEN(F22)-2)/1000</f>
-        <v>0.06</v>
+        <v>0.35</v>
       </c>
       <c r="I22" s="45">
         <f>LEFT(E22,LEN(E22)-4)+0</f>
-        <v>170</v>
+        <v>611</v>
       </c>
       <c r="J22" s="38">
-        <f t="shared" si="0"/>
-        <v>50.999999999999993</v>
+        <f>G22*60^2/H22</f>
+        <v>11.005714285714285</v>
       </c>
       <c r="K22" s="55">
-        <f t="shared" si="1"/>
-        <v>0.29999999999999993</v>
+        <f>J22/I22</f>
+        <v>1.801262567220014E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B23" s="50" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C23" s="51">
-        <v>4.5999999999999996</v>
+        <v>3.43</v>
       </c>
       <c r="D23" s="51">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="E23" s="52" t="s">
-        <v>452</v>
+        <v>511</v>
       </c>
       <c r="F23" s="53" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G23" s="54">
         <f>C23/1000</f>
-        <v>4.5999999999999999E-3</v>
+        <v>3.4300000000000003E-3</v>
       </c>
       <c r="H23" s="54">
         <f>LEFT(F23,LEN(F23)-2)/1000</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="I23" s="54">
         <f>LEFT(E23,LEN(E23)-4)+0</f>
-        <v>1041</v>
+        <v>2895</v>
       </c>
       <c r="J23" s="38">
-        <f t="shared" si="0"/>
-        <v>66.239999999999995</v>
+        <f>G23*60^2/H23</f>
+        <v>41.160000000000004</v>
       </c>
       <c r="K23" s="55">
-        <f t="shared" si="1"/>
-        <v>6.3631123919308349E-2</v>
+        <f>J23/I23</f>
+        <v>1.4217616580310882E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="56" t="s">
         <v>516</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K1" xr:uid="{23B363DB-B5F4-41D8-9D8E-D3A12DB8292F}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K24">
+      <sortCondition descending="1" ref="K1"/>
+    </sortState>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J23">
     <sortCondition ref="D2:D23"/>
     <sortCondition descending="1" ref="C2:C23"/>
   </sortState>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A24" r:id="rId1" xr:uid="{BB7EF3AA-2EF4-4AD5-B795-3D60D77527D2}"/>
   </hyperlinks>
@@ -14063,20 +14067,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CF7E297-E838-4A38-A980-0D0CB35E9F41}">
   <dimension ref="A2:N37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="28.33203125" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" customWidth="1"/>
-    <col min="13" max="13" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" customWidth="1"/>
+    <col min="10" max="10" width="9.5546875" customWidth="1"/>
+    <col min="13" max="13" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="I2" t="s">
@@ -14086,7 +14090,7 @@
         <v>1.2549999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="5" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" s="5" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -14125,7 +14129,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="5" customFormat="1" ht="12.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" s="5" customFormat="1" ht="12.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>34</v>
       </c>
@@ -14163,15 +14167,15 @@
         <v>410</v>
       </c>
       <c r="M4" s="11">
-        <f>K4*60^2/(L4*1/1000)</f>
+        <f t="shared" ref="M4:M20" si="0">K4*60^2/(L4*1/1000)</f>
         <v>1404.8780487804879</v>
       </c>
       <c r="N4" s="12">
-        <f>IFERROR(M4/J4,0)</f>
+        <f t="shared" ref="N4:N20" si="1">IFERROR(M4/J4,0)</f>
         <v>7.7191101581345487</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>17</v>
       </c>
@@ -14207,15 +14211,15 @@
         <v>900</v>
       </c>
       <c r="M5" s="11">
-        <f>K5*60^2/(L5*1/1000)</f>
+        <f t="shared" si="0"/>
         <v>8400</v>
       </c>
       <c r="N5" s="12">
-        <f>IFERROR(M5/J5,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>19</v>
       </c>
@@ -14253,15 +14257,15 @@
         <v>1000</v>
       </c>
       <c r="M6" s="11">
-        <f>K6*60^2/(L6*1/1000)</f>
+        <f t="shared" si="0"/>
         <v>8640</v>
       </c>
       <c r="N6" s="12">
-        <f>IFERROR(M6/J6,0)</f>
+        <f t="shared" si="1"/>
         <v>5.2205438066465257</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>32</v>
       </c>
@@ -14299,15 +14303,15 @@
         <v>1100</v>
       </c>
       <c r="M7" s="11">
-        <f>K7*60^2/(L7*1/1000)</f>
+        <f t="shared" si="0"/>
         <v>1047.2727272727273</v>
       </c>
       <c r="N7" s="12">
-        <f>IFERROR(M7/J7,0)</f>
+        <f t="shared" si="1"/>
         <v>1.1023923444976076</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>7</v>
       </c>
@@ -14346,15 +14350,15 @@
         <v>180</v>
       </c>
       <c r="M8" s="11">
-        <f>K8*60^2/(L8*1/1000)</f>
+        <f t="shared" si="0"/>
         <v>6800</v>
       </c>
       <c r="N8" s="12">
-        <f>IFERROR(M8/J8,0)</f>
+        <f t="shared" si="1"/>
         <v>9.0305444887118203</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>10</v>
       </c>
@@ -14392,15 +14396,15 @@
         <v>500</v>
       </c>
       <c r="M9" s="11">
-        <f>K9*60^2/(L9*1/1000)</f>
+        <f t="shared" si="0"/>
         <v>8640</v>
       </c>
       <c r="N9" s="12">
-        <f>IFERROR(M9/J9,0)</f>
+        <f t="shared" si="1"/>
         <v>4.32</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>31</v>
       </c>
@@ -14436,15 +14440,15 @@
         <v>2100</v>
       </c>
       <c r="M10" s="11">
-        <f>K10*60^2/(L10*1/1000)</f>
+        <f t="shared" si="0"/>
         <v>10285.714285714284</v>
       </c>
       <c r="N10" s="12">
-        <f>IFERROR(M10/J10,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>28</v>
       </c>
@@ -14480,15 +14484,15 @@
         <v>2100</v>
       </c>
       <c r="M11" s="11">
-        <f>K11*60^2/(L11*1/1000)</f>
+        <f t="shared" si="0"/>
         <v>10285.714285714284</v>
       </c>
       <c r="N11" s="12">
-        <f>IFERROR(M11/J11,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>22</v>
       </c>
@@ -14527,15 +14531,15 @@
         <v>1230</v>
       </c>
       <c r="M12" s="11">
-        <f>K12*60^2/(L12*1/1000)</f>
+        <f t="shared" si="0"/>
         <v>8195.121951219513</v>
       </c>
       <c r="N12" s="12">
-        <f>IFERROR(M12/J12,0)</f>
+        <f t="shared" si="1"/>
         <v>4.5034328623269753</v>
       </c>
     </row>
-    <row r="13" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>20</v>
       </c>
@@ -14573,15 +14577,15 @@
         <v>980</v>
       </c>
       <c r="M13" s="11">
-        <f>K13*60^2/(L13*1/1000)</f>
+        <f t="shared" si="0"/>
         <v>11387.755102040817</v>
       </c>
       <c r="N13" s="12">
-        <f>IFERROR(M13/J13,0)</f>
+        <f t="shared" si="1"/>
         <v>7.591836734693878</v>
       </c>
     </row>
-    <row r="14" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>37</v>
       </c>
@@ -14619,15 +14623,15 @@
         <v>2100</v>
       </c>
       <c r="M14" s="11">
-        <f>K14*60^2/(L14*1/1000)</f>
+        <f t="shared" si="0"/>
         <v>12000</v>
       </c>
       <c r="N14" s="12">
-        <f>IFERROR(M14/J14,0)</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>23</v>
       </c>
@@ -14665,15 +14669,15 @@
         <v>1410</v>
       </c>
       <c r="M15" s="11">
-        <f>K15*60^2/(L15*1/1000)</f>
+        <f t="shared" si="0"/>
         <v>19914.893617021276</v>
       </c>
       <c r="N15" s="12">
-        <f>IFERROR(M15/J15,0)</f>
+        <f t="shared" si="1"/>
         <v>79.659574468085111</v>
       </c>
     </row>
-    <row r="16" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>25</v>
       </c>
@@ -14711,15 +14715,15 @@
         <v>1600</v>
       </c>
       <c r="M16" s="11">
-        <f>K16*60^2/(L16*1/1000)</f>
+        <f t="shared" si="0"/>
         <v>24750</v>
       </c>
       <c r="N16" s="12">
-        <f>IFERROR(M16/J16,0)</f>
+        <f t="shared" si="1"/>
         <v>28.285714285714285</v>
       </c>
     </row>
-    <row r="17" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>27</v>
       </c>
@@ -14757,15 +14761,15 @@
         <v>1850</v>
       </c>
       <c r="M17" s="11">
-        <f>K17*60^2/(L17*1/1000)</f>
+        <f t="shared" si="0"/>
         <v>24908.108108108107</v>
       </c>
       <c r="N17" s="12">
-        <f>IFERROR(M17/J17,0)</f>
+        <f t="shared" si="1"/>
         <v>15.281047919084727</v>
       </c>
     </row>
-    <row r="18" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>13</v>
       </c>
@@ -14804,15 +14808,15 @@
         <v>2200</v>
       </c>
       <c r="M18" s="11">
-        <f>K18*60^2/(L18*1/1000)</f>
+        <f t="shared" si="0"/>
         <v>78545.454545454544</v>
       </c>
       <c r="N18" s="12">
-        <f>IFERROR(M18/J18,0)</f>
+        <f t="shared" si="1"/>
         <v>73.630611244860134</v>
       </c>
     </row>
-    <row r="19" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>15</v>
       </c>
@@ -14851,15 +14855,15 @@
         <v>1800</v>
       </c>
       <c r="M19" s="11">
-        <f>K19*60^2/(L19*1/1000)</f>
+        <f t="shared" si="0"/>
         <v>68000</v>
       </c>
       <c r="N19" s="12">
-        <f>IFERROR(M19/J19,0)</f>
+        <f t="shared" si="1"/>
         <v>40.135753283163645</v>
       </c>
     </row>
-    <row r="20" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>11</v>
       </c>
@@ -14898,19 +14902,19 @@
         <v>2200</v>
       </c>
       <c r="M20" s="11">
-        <f>K20*60^2/(L20*1/1000)</f>
+        <f t="shared" si="0"/>
         <v>85090.909090909088</v>
       </c>
       <c r="N20" s="12">
-        <f>IFERROR(M20/J20,0)</f>
+        <f t="shared" si="1"/>
         <v>75.335023542194861</v>
       </c>
     </row>
-    <row r="21" spans="1:14" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
     </row>
-    <row r="22" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="D22"/>
@@ -14921,7 +14925,7 @@
       <c r="I22"/>
       <c r="J22"/>
     </row>
-    <row r="23" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="D23"/>
@@ -14932,7 +14936,7 @@
       <c r="I23"/>
       <c r="J23"/>
     </row>
-    <row r="24" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="D24"/>
@@ -14943,7 +14947,7 @@
       <c r="I24"/>
       <c r="J24"/>
     </row>
-    <row r="25" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="D25"/>
@@ -14954,7 +14958,7 @@
       <c r="I25"/>
       <c r="J25"/>
     </row>
-    <row r="26" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="D26"/>
@@ -14965,7 +14969,7 @@
       <c r="I26"/>
       <c r="J26"/>
     </row>
-    <row r="27" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="D27"/>
@@ -14976,7 +14980,7 @@
       <c r="I27"/>
       <c r="J27"/>
     </row>
-    <row r="28" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="D28"/>
@@ -14987,7 +14991,7 @@
       <c r="I28"/>
       <c r="J28"/>
     </row>
-    <row r="29" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="D29"/>
@@ -14998,7 +15002,7 @@
       <c r="I29"/>
       <c r="J29"/>
     </row>
-    <row r="30" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="D30"/>
@@ -15009,7 +15013,7 @@
       <c r="I30"/>
       <c r="J30"/>
     </row>
-    <row r="31" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="D31"/>
@@ -15020,7 +15024,7 @@
       <c r="I31"/>
       <c r="J31"/>
     </row>
-    <row r="32" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="D32"/>
@@ -15031,7 +15035,7 @@
       <c r="I32"/>
       <c r="J32"/>
     </row>
-    <row r="33" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="D33"/>
@@ -15042,7 +15046,7 @@
       <c r="I33"/>
       <c r="J33"/>
     </row>
-    <row r="34" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="D34"/>
@@ -15053,7 +15057,7 @@
       <c r="I34"/>
       <c r="J34"/>
     </row>
-    <row r="35" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="D35"/>
@@ -15064,7 +15068,7 @@
       <c r="I35"/>
       <c r="J35"/>
     </row>
-    <row r="36" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="D36"/>
@@ -15075,7 +15079,7 @@
       <c r="I36"/>
       <c r="J36"/>
     </row>
-    <row r="37" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="D37"/>
@@ -15122,292 +15126,331 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8F5E4B-FCDD-4425-BBCA-0D6AD947D2E5}">
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12.21875" customWidth="1"/>
+    <col min="3" max="3" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" customWidth="1"/>
+    <col min="8" max="8" width="26.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>438</v>
       </c>
       <c r="B1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C1" t="s">
         <v>443</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>439</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>444</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>442</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>441</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="27">
         <v>42370</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="59">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
         <v>518</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>1080</v>
       </c>
-      <c r="D2">
-        <v>619</v>
-      </c>
-      <c r="E2" s="58">
+      <c r="E2">
+        <v>600</v>
+      </c>
+      <c r="F2" s="58">
         <v>0.18</v>
       </c>
-      <c r="F2" s="57">
+      <c r="G2" s="57">
         <v>3.0899999999999999E-3</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="27">
         <v>42370</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="59">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
         <v>518</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1070</v>
       </c>
-      <c r="D3">
-        <v>246</v>
-      </c>
-      <c r="E3" s="58">
+      <c r="E3">
+        <v>379</v>
+      </c>
+      <c r="F3" s="58">
         <v>0.15</v>
       </c>
-      <c r="F3" s="57">
+      <c r="G3" s="57">
         <v>2.8300000000000001E-3</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="27">
-        <v>42736</v>
-      </c>
-      <c r="B4" t="s">
+        <v>42804</v>
+      </c>
+      <c r="B4" s="59">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
         <v>518</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>517</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>1041</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0.25</v>
       </c>
-      <c r="F4" s="57">
+      <c r="G4" s="57">
         <v>4.5999999999999999E-3</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="27">
         <v>43101</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="59">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
         <v>440</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>110</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>182</v>
       </c>
-      <c r="E5" s="58">
+      <c r="F5" s="58">
         <v>0.41</v>
       </c>
-      <c r="F5" s="57">
+      <c r="G5" s="57">
         <v>0.16</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="27">
         <v>43191</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="59">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s">
         <v>440</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>108</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>1655</v>
       </c>
-      <c r="E6" s="58">
+      <c r="F6" s="58">
         <v>1</v>
       </c>
-      <c r="F6" s="57">
+      <c r="G6" s="57">
         <v>2.4</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="27">
         <v>43252</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="59">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s">
         <v>440</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>102</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>2000</v>
       </c>
-      <c r="E7" s="58">
+      <c r="F7" s="58">
         <v>0.5</v>
       </c>
-      <c r="F7" s="57">
+      <c r="G7" s="57">
         <v>1.2</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="27">
         <v>43313</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="59">
+        <v>0</v>
+      </c>
+      <c r="C8" t="s">
         <v>440</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>106</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>1500</v>
       </c>
-      <c r="E8" s="58">
+      <c r="F8" s="58">
         <v>2.1</v>
       </c>
-      <c r="F8" s="57">
+      <c r="G8" s="57">
         <v>7</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="27">
         <v>43374</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="59">
+        <v>0</v>
+      </c>
+      <c r="C9" t="s">
         <v>440</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>97</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>1630</v>
       </c>
-      <c r="E9" s="58">
+      <c r="F9" s="58">
         <v>1.85</v>
       </c>
-      <c r="F9" s="57">
+      <c r="G9" s="57">
         <v>12.8</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="27">
         <v>43405</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="59">
+        <v>0</v>
+      </c>
+      <c r="C10" t="s">
         <v>440</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>99</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>1070</v>
       </c>
-      <c r="E10" s="58">
+      <c r="F10" s="58">
         <v>2.2000000000000002</v>
       </c>
-      <c r="F10" s="57">
+      <c r="G10" s="57">
         <v>48</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="27">
         <v>43647</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="59">
+        <v>0</v>
+      </c>
+      <c r="C11" t="s">
         <v>440</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>96</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>1130</v>
       </c>
-      <c r="E11" s="58">
+      <c r="F11" s="58">
         <v>2.2000000000000002</v>
       </c>
-      <c r="F11" s="57">
+      <c r="G11" s="57">
         <v>52</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="27"/>
+      <c r="B13" s="27"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="27"/>
+      <c r="B14" s="27"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="27"/>
+      <c r="B15" s="27"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="27"/>
+      <c r="B16" s="27"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="27"/>
+      <c r="B17" s="27"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G11" xr:uid="{5BD1D22B-1577-4E54-B961-9F3A5834CBCA}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G11">
+  <autoFilter ref="A1:H11" xr:uid="{5BD1D22B-1577-4E54-B961-9F3A5834CBCA}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H11">
       <sortCondition ref="A1:A11"/>
     </sortState>
   </autoFilter>
@@ -15418,17 +15461,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{954EE39A-810C-41EE-AD59-94610CD98D48}">
   <dimension ref="B2:N85"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" s="13" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:14" s="13" customFormat="1" ht="10.199999999999999" x14ac:dyDescent="0.2">
       <c r="K2" s="13" t="s">
         <v>435</v>
       </c>
@@ -15442,7 +15485,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="3" spans="2:14" s="13" customFormat="1" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:14" s="13" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="14" t="s">
         <v>220</v>
       </c>
@@ -15465,15 +15508,15 @@
         <v>434</v>
       </c>
       <c r="I3" s="13">
-        <f>LEFT(D3,LEN(D3)-4)+0</f>
+        <f t="shared" ref="I3:I34" si="0">LEFT(D3,LEN(D3)-4)+0</f>
         <v>110</v>
       </c>
       <c r="J3" s="13" t="str">
-        <f>LEFT(RIGHT(D3,4),1)</f>
+        <f t="shared" ref="J3:J34" si="1">LEFT(RIGHT(D3,4),1)</f>
         <v>T</v>
       </c>
       <c r="K3" s="13">
-        <f>IF(J3="T",I3,I3/1000)</f>
+        <f t="shared" ref="K3:K34" si="2">IF(J3="T",I3,I3/1000)</f>
         <v>110</v>
       </c>
       <c r="L3" s="13">
@@ -15489,7 +15532,7 @@
         <v>43952</v>
       </c>
     </row>
-    <row r="4" spans="2:14" s="13" customFormat="1" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" s="13" customFormat="1" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14" t="s">
         <v>218</v>
       </c>
@@ -15512,31 +15555,31 @@
         <v>432</v>
       </c>
       <c r="I4" s="13">
-        <f>LEFT(D4,LEN(D4)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>95</v>
       </c>
       <c r="J4" s="13" t="str">
-        <f>LEFT(RIGHT(D4,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K4" s="13">
-        <f>IF(J4="T",I4,I4/1000)</f>
+        <f t="shared" si="2"/>
         <v>95</v>
       </c>
       <c r="L4" s="13">
-        <f t="shared" ref="L4:L67" si="0">LEFT(E4,LEN(E4)-1)+0</f>
+        <f t="shared" ref="L4:L67" si="3">LEFT(E4,LEN(E4)-1)+0</f>
         <v>3250</v>
       </c>
       <c r="M4" s="11">
-        <f t="shared" ref="M4:M67" si="1">K4*60^2/(L4*1/1000)</f>
+        <f t="shared" ref="M4:M67" si="4">K4*60^2/(L4*1/1000)</f>
         <v>105230.76923076923</v>
       </c>
       <c r="N4" s="26">
-        <f t="shared" ref="N4:N67" si="2">DATE(RIGHT(C4,4)+0,MONTH(1&amp;LEFT(LEFT(C4,3),3)),1)</f>
+        <f t="shared" ref="N4:N67" si="5">DATE(RIGHT(C4,4)+0,MONTH(1&amp;LEFT(LEFT(C4,3),3)),1)</f>
         <v>43952</v>
       </c>
     </row>
-    <row r="5" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
         <v>217</v>
       </c>
@@ -15559,31 +15602,31 @@
         <v>430</v>
       </c>
       <c r="I5" s="13">
-        <f>LEFT(D5,LEN(D5)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>86</v>
       </c>
       <c r="J5" s="13" t="str">
-        <f>LEFT(RIGHT(D5,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K5" s="13">
-        <f>IF(J5="T",I5,I5/1000)</f>
+        <f t="shared" si="2"/>
         <v>86</v>
       </c>
       <c r="L5" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3268</v>
       </c>
       <c r="M5" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>94736.84210526316</v>
       </c>
       <c r="N5" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43922</v>
       </c>
     </row>
-    <row r="6" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B6" s="14" t="s">
         <v>216</v>
       </c>
@@ -15606,31 +15649,31 @@
         <v>427</v>
       </c>
       <c r="I6" s="13">
-        <f>LEFT(D6,LEN(D6)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>80</v>
       </c>
       <c r="J6" s="13" t="str">
-        <f>LEFT(RIGHT(D6,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K6" s="13">
-        <f>IF(J6="T",I6,I6/1000)</f>
+        <f t="shared" si="2"/>
         <v>80</v>
       </c>
       <c r="L6" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6300</v>
       </c>
       <c r="M6" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>45714.285714285717</v>
       </c>
       <c r="N6" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43405</v>
       </c>
     </row>
-    <row r="7" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
         <v>215</v>
       </c>
@@ -15653,31 +15696,31 @@
         <v>424</v>
       </c>
       <c r="I7" s="13">
-        <f>LEFT(D7,LEN(D7)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>76</v>
       </c>
       <c r="J7" s="13" t="str">
-        <f>LEFT(RIGHT(D7,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K7" s="13">
-        <f>IF(J7="T",I7,I7/1000)</f>
+        <f t="shared" si="2"/>
         <v>76</v>
       </c>
       <c r="L7" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>4000</v>
       </c>
       <c r="M7" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>68400</v>
       </c>
       <c r="N7" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43221</v>
       </c>
     </row>
-    <row r="8" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B8" s="14" t="s">
         <v>214</v>
       </c>
@@ -15700,31 +15743,31 @@
         <v>421</v>
       </c>
       <c r="I8" s="13">
-        <f>LEFT(D8,LEN(D8)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>73</v>
       </c>
       <c r="J8" s="13" t="str">
-        <f>LEFT(RIGHT(D8,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K8" s="13">
-        <f>IF(J8="T",I8,I8/1000)</f>
+        <f t="shared" si="2"/>
         <v>73</v>
       </c>
       <c r="L8" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2920</v>
       </c>
       <c r="M8" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>90000</v>
       </c>
       <c r="N8" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43800</v>
       </c>
     </row>
-    <row r="9" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B9" s="14" t="s">
         <v>212</v>
       </c>
@@ -15747,31 +15790,31 @@
         <v>418</v>
       </c>
       <c r="I9" s="13">
-        <f>LEFT(D9,LEN(D9)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>70</v>
       </c>
       <c r="J9" s="13" t="str">
-        <f>LEFT(RIGHT(D9,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K9" s="13">
-        <f>IF(J9="T",I9,I9/1000)</f>
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
       <c r="L9" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3220</v>
       </c>
       <c r="M9" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>78260.869565217392</v>
       </c>
       <c r="N9" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43922</v>
       </c>
     </row>
-    <row r="10" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B10" s="14" t="s">
         <v>211</v>
       </c>
@@ -15794,31 +15837,31 @@
         <v>415</v>
       </c>
       <c r="I10" s="13">
-        <f>LEFT(D10,LEN(D10)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="J10" s="13" t="str">
-        <f>LEFT(RIGHT(D10,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K10" s="13">
-        <f>IF(J10="T",I10,I10/1000)</f>
+        <f t="shared" si="2"/>
         <v>68</v>
       </c>
       <c r="L10" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3360</v>
       </c>
       <c r="M10" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>72857.142857142855</v>
       </c>
       <c r="N10" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43678</v>
       </c>
     </row>
-    <row r="11" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>209</v>
       </c>
@@ -15841,31 +15884,31 @@
         <v>411</v>
       </c>
       <c r="I11" s="13">
-        <f>LEFT(D11,LEN(D11)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="J11" s="13" t="str">
-        <f>LEFT(RIGHT(D11,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K11" s="13">
-        <f>IF(J11="T",I11,I11/1000)</f>
+        <f t="shared" si="2"/>
         <v>64</v>
       </c>
       <c r="L11" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2880</v>
       </c>
       <c r="M11" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>80000</v>
       </c>
       <c r="N11" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43770</v>
       </c>
     </row>
-    <row r="12" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B12" s="14" t="s">
         <v>210</v>
       </c>
@@ -15888,31 +15931,31 @@
         <v>413</v>
       </c>
       <c r="I12" s="13">
-        <f>LEFT(D12,LEN(D12)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="J12" s="13" t="str">
-        <f>LEFT(RIGHT(D12,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K12" s="13">
-        <f>IF(J12="T",I12,I12/1000)</f>
+        <f t="shared" si="2"/>
         <v>64</v>
       </c>
       <c r="L12" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3200</v>
       </c>
       <c r="M12" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>72000</v>
       </c>
       <c r="N12" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43800</v>
       </c>
     </row>
-    <row r="13" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
         <v>208</v>
       </c>
@@ -15935,31 +15978,31 @@
         <v>408</v>
       </c>
       <c r="I13" s="13">
-        <f>LEFT(D13,LEN(D13)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="J13" s="13" t="str">
-        <f>LEFT(RIGHT(D13,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K13" s="13">
-        <f>IF(J13="T",I13,I13/1000)</f>
+        <f t="shared" si="2"/>
         <v>60</v>
       </c>
       <c r="L13" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2800</v>
       </c>
       <c r="M13" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>77142.857142857145</v>
       </c>
       <c r="N13" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43709</v>
       </c>
     </row>
-    <row r="14" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B14" s="14" t="s">
         <v>206</v>
       </c>
@@ -15982,31 +16025,31 @@
         <v>406</v>
       </c>
       <c r="I14" s="13">
-        <f>LEFT(D14,LEN(D14)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="J14" s="13" t="str">
-        <f>LEFT(RIGHT(D14,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K14" s="13">
-        <f>IF(J14="T",I14,I14/1000)</f>
+        <f t="shared" si="2"/>
         <v>58</v>
       </c>
       <c r="L14" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2500</v>
       </c>
       <c r="M14" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>83520</v>
       </c>
       <c r="N14" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43800</v>
       </c>
     </row>
-    <row r="15" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B15" s="14" t="s">
         <v>205</v>
       </c>
@@ -16029,31 +16072,31 @@
         <v>404</v>
       </c>
       <c r="I15" s="13">
-        <f>LEFT(D15,LEN(D15)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="J15" s="13" t="str">
-        <f>LEFT(RIGHT(D15,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K15" s="13">
-        <f>IF(J15="T",I15,I15/1000)</f>
+        <f t="shared" si="2"/>
         <v>57</v>
       </c>
       <c r="L15" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3300</v>
       </c>
       <c r="M15" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>62181.818181818184</v>
       </c>
       <c r="N15" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43709</v>
       </c>
     </row>
-    <row r="16" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B16" s="14" t="s">
         <v>202</v>
       </c>
@@ -16076,31 +16119,31 @@
         <v>399</v>
       </c>
       <c r="I16" s="13">
-        <f>LEFT(D16,LEN(D16)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="J16" s="13" t="str">
-        <f>LEFT(RIGHT(D16,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K16" s="13">
-        <f>IF(J16="T",I16,I16/1000)</f>
+        <f t="shared" si="2"/>
         <v>56</v>
       </c>
       <c r="L16" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2520</v>
       </c>
       <c r="M16" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>80000</v>
       </c>
       <c r="N16" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43556</v>
       </c>
     </row>
-    <row r="17" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B17" s="14" t="s">
         <v>203</v>
       </c>
@@ -16123,31 +16166,31 @@
         <v>401</v>
       </c>
       <c r="I17" s="13">
-        <f>LEFT(D17,LEN(D17)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="J17" s="13" t="str">
-        <f>LEFT(RIGHT(D17,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K17" s="13">
-        <f>IF(J17="T",I17,I17/1000)</f>
+        <f t="shared" si="2"/>
         <v>56</v>
       </c>
       <c r="L17" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3360</v>
       </c>
       <c r="M17" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>60000</v>
       </c>
       <c r="N17" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43617</v>
       </c>
     </row>
-    <row r="18" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B18" s="14" t="s">
         <v>201</v>
       </c>
@@ -16170,31 +16213,31 @@
         <v>396</v>
       </c>
       <c r="I18" s="13">
-        <f>LEFT(D18,LEN(D18)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="J18" s="13" t="str">
-        <f>LEFT(RIGHT(D18,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K18" s="13">
-        <f>IF(J18="T",I18,I18/1000)</f>
+        <f t="shared" si="2"/>
         <v>55</v>
       </c>
       <c r="L18" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3500</v>
       </c>
       <c r="M18" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>56571.428571428572</v>
       </c>
       <c r="N18" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43344</v>
       </c>
     </row>
-    <row r="19" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B19" s="14" t="s">
         <v>197</v>
       </c>
@@ -16217,31 +16260,31 @@
         <v>388</v>
       </c>
       <c r="I19" s="13">
-        <f>LEFT(D19,LEN(D19)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="J19" s="13" t="str">
-        <f>LEFT(RIGHT(D19,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K19" s="13">
-        <f>IF(J19="T",I19,I19/1000)</f>
+        <f t="shared" si="2"/>
         <v>53</v>
       </c>
       <c r="L19" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2094</v>
       </c>
       <c r="M19" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>91117.478510028654</v>
       </c>
       <c r="N19" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43556</v>
       </c>
     </row>
-    <row r="20" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B20" s="14" t="s">
         <v>198</v>
       </c>
@@ -16264,31 +16307,31 @@
         <v>390</v>
       </c>
       <c r="I20" s="13">
-        <f>LEFT(D20,LEN(D20)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="J20" s="13" t="str">
-        <f>LEFT(RIGHT(D20,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K20" s="13">
-        <f>IF(J20="T",I20,I20/1000)</f>
+        <f t="shared" si="2"/>
         <v>53</v>
       </c>
       <c r="L20" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2385</v>
       </c>
       <c r="M20" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>80000</v>
       </c>
       <c r="N20" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43556</v>
       </c>
     </row>
-    <row r="21" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B21" s="14" t="s">
         <v>199</v>
       </c>
@@ -16311,31 +16354,31 @@
         <v>393</v>
       </c>
       <c r="I21" s="13">
-        <f>LEFT(D21,LEN(D21)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="J21" s="13" t="str">
-        <f>LEFT(RIGHT(D21,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K21" s="13">
-        <f>IF(J21="T",I21,I21/1000)</f>
+        <f t="shared" si="2"/>
         <v>53</v>
       </c>
       <c r="L21" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2915</v>
       </c>
       <c r="M21" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>65454.545454545456</v>
       </c>
       <c r="N21" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43770</v>
       </c>
     </row>
-    <row r="22" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B22" s="14" t="s">
         <v>196</v>
       </c>
@@ -16358,31 +16401,31 @@
         <v>385</v>
       </c>
       <c r="I22" s="13">
-        <f>LEFT(D22,LEN(D22)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="J22" s="13" t="str">
-        <f>LEFT(RIGHT(D22,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K22" s="13">
-        <f>IF(J22="T",I22,I22/1000)</f>
+        <f t="shared" si="2"/>
         <v>52</v>
       </c>
       <c r="L22" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2800</v>
       </c>
       <c r="M22" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>66857.142857142855</v>
       </c>
       <c r="N22" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43586</v>
       </c>
     </row>
-    <row r="23" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B23" s="14" t="s">
         <v>191</v>
       </c>
@@ -16405,31 +16448,31 @@
         <v>377</v>
       </c>
       <c r="I23" s="13">
-        <f>LEFT(D23,LEN(D23)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="J23" s="13" t="str">
-        <f>LEFT(RIGHT(D23,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K23" s="13">
-        <f>IF(J23="T",I23,I23/1000)</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="L23" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1975</v>
       </c>
       <c r="M23" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>91139.240506329108</v>
       </c>
       <c r="N23" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43556</v>
       </c>
     </row>
-    <row r="24" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B24" s="14" t="s">
         <v>193</v>
       </c>
@@ -16452,31 +16495,31 @@
         <v>378</v>
       </c>
       <c r="I24" s="13">
-        <f>LEFT(D24,LEN(D24)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="J24" s="13" t="str">
-        <f>LEFT(RIGHT(D24,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K24" s="13">
-        <f>IF(J24="T",I24,I24/1000)</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="L24" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2500</v>
       </c>
       <c r="M24" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>72000</v>
       </c>
       <c r="N24" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43709</v>
       </c>
     </row>
-    <row r="25" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B25" s="14" t="s">
         <v>194</v>
       </c>
@@ -16499,31 +16542,31 @@
         <v>380</v>
       </c>
       <c r="I25" s="13">
-        <f>LEFT(D25,LEN(D25)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="J25" s="13" t="str">
-        <f>LEFT(RIGHT(D25,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K25" s="13">
-        <f>IF(J25="T",I25,I25/1000)</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="L25" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3100</v>
       </c>
       <c r="M25" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>58064.516129032258</v>
       </c>
       <c r="N25" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43647</v>
       </c>
     </row>
-    <row r="26" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B26" s="14" t="s">
         <v>195</v>
       </c>
@@ -16546,31 +16589,31 @@
         <v>382</v>
       </c>
       <c r="I26" s="13">
-        <f>LEFT(D26,LEN(D26)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="J26" s="13" t="str">
-        <f>LEFT(RIGHT(D26,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K26" s="13">
-        <f>IF(J26="T",I26,I26/1000)</f>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="L26" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3250</v>
       </c>
       <c r="M26" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>55384.615384615383</v>
       </c>
       <c r="N26" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43709</v>
       </c>
     </row>
-    <row r="27" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B27" s="14" t="s">
         <v>188</v>
       </c>
@@ -16593,31 +16636,31 @@
         <v>372</v>
       </c>
       <c r="I27" s="13">
-        <f>LEFT(D27,LEN(D27)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="J27" s="13" t="str">
-        <f>LEFT(RIGHT(D27,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K27" s="13">
-        <f>IF(J27="T",I27,I27/1000)</f>
+        <f t="shared" si="2"/>
         <v>49</v>
       </c>
       <c r="L27" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>5400</v>
       </c>
       <c r="M27" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>32666.666666666664</v>
       </c>
       <c r="N27" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43101</v>
       </c>
     </row>
-    <row r="28" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B28" s="14" t="s">
         <v>189</v>
       </c>
@@ -16640,31 +16683,31 @@
         <v>374</v>
       </c>
       <c r="I28" s="13">
-        <f>LEFT(D28,LEN(D28)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="J28" s="13" t="str">
-        <f>LEFT(RIGHT(D28,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K28" s="13">
-        <f>IF(J28="T",I28,I28/1000)</f>
+        <f t="shared" si="2"/>
         <v>49</v>
       </c>
       <c r="L28" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6400</v>
       </c>
       <c r="M28" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>27562.5</v>
       </c>
       <c r="N28" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43070</v>
       </c>
     </row>
-    <row r="29" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B29" s="14" t="s">
         <v>187</v>
       </c>
@@ -16687,31 +16730,31 @@
         <v>369</v>
       </c>
       <c r="I29" s="13">
-        <f>LEFT(D29,LEN(D29)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="J29" s="13" t="str">
-        <f>LEFT(RIGHT(D29,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K29" s="13">
-        <f>IF(J29="T",I29,I29/1000)</f>
+        <f t="shared" si="2"/>
         <v>46</v>
       </c>
       <c r="L29" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2100</v>
       </c>
       <c r="M29" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>78857.142857142855</v>
       </c>
       <c r="N29" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43647</v>
       </c>
     </row>
-    <row r="30" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B30" s="14" t="s">
         <v>184</v>
       </c>
@@ -16734,31 +16777,31 @@
         <v>363</v>
       </c>
       <c r="I30" s="13">
-        <f>LEFT(D30,LEN(D30)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="J30" s="13" t="str">
-        <f>LEFT(RIGHT(D30,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K30" s="13">
-        <f>IF(J30="T",I30,I30/1000)</f>
+        <f t="shared" si="2"/>
         <v>44</v>
       </c>
       <c r="L30" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1980</v>
       </c>
       <c r="M30" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>80000</v>
       </c>
       <c r="N30" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43374</v>
       </c>
     </row>
-    <row r="31" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B31" s="14" t="s">
         <v>185</v>
       </c>
@@ -16781,31 +16824,31 @@
         <v>365</v>
       </c>
       <c r="I31" s="13">
-        <f>LEFT(D31,LEN(D31)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="J31" s="13" t="str">
-        <f>LEFT(RIGHT(D31,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K31" s="13">
-        <f>IF(J31="T",I31,I31/1000)</f>
+        <f t="shared" si="2"/>
         <v>44</v>
       </c>
       <c r="L31" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2100</v>
       </c>
       <c r="M31" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>75428.57142857142</v>
       </c>
       <c r="N31" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43374</v>
       </c>
     </row>
-    <row r="32" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B32" s="14" t="s">
         <v>186</v>
       </c>
@@ -16828,31 +16871,31 @@
         <v>367</v>
       </c>
       <c r="I32" s="13">
-        <f>LEFT(D32,LEN(D32)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="J32" s="13" t="str">
-        <f>LEFT(RIGHT(D32,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K32" s="13">
-        <f>IF(J32="T",I32,I32/1000)</f>
+        <f t="shared" si="2"/>
         <v>44</v>
       </c>
       <c r="L32" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2500</v>
       </c>
       <c r="M32" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>63360</v>
       </c>
       <c r="N32" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43709</v>
       </c>
     </row>
-    <row r="33" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B33" s="14" t="s">
         <v>182</v>
       </c>
@@ -16875,31 +16918,31 @@
         <v>361</v>
       </c>
       <c r="I33" s="13">
-        <f>LEFT(D33,LEN(D33)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="J33" s="13" t="str">
-        <f>LEFT(RIGHT(D33,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K33" s="13">
-        <f>IF(J33="T",I33,I33/1000)</f>
+        <f t="shared" si="2"/>
         <v>43</v>
       </c>
       <c r="L33" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2100</v>
       </c>
       <c r="M33" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>73714.28571428571</v>
       </c>
       <c r="N33" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43466</v>
       </c>
     </row>
-    <row r="34" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B34" s="14" t="s">
         <v>180</v>
       </c>
@@ -16922,31 +16965,31 @@
         <v>352</v>
       </c>
       <c r="I34" s="13">
-        <f>LEFT(D34,LEN(D34)-4)+0</f>
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="J34" s="13" t="str">
-        <f>LEFT(RIGHT(D34,4),1)</f>
+        <f t="shared" si="1"/>
         <v>T</v>
       </c>
       <c r="K34" s="13">
-        <f>IF(J34="T",I34,I34/1000)</f>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="L34" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2200</v>
       </c>
       <c r="M34" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>65454.545454545449</v>
       </c>
       <c r="N34" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43586</v>
       </c>
     </row>
-    <row r="35" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B35" s="14" t="s">
         <v>178</v>
       </c>
@@ -16969,31 +17012,31 @@
         <v>357</v>
       </c>
       <c r="I35" s="13">
-        <f>LEFT(D35,LEN(D35)-4)+0</f>
+        <f t="shared" ref="I35:I66" si="6">LEFT(D35,LEN(D35)-4)+0</f>
         <v>39</v>
       </c>
       <c r="J35" s="13" t="str">
-        <f>LEFT(RIGHT(D35,4),1)</f>
+        <f t="shared" ref="J35:J66" si="7">LEFT(RIGHT(D35,4),1)</f>
         <v>T</v>
       </c>
       <c r="K35" s="13">
-        <f>IF(J35="T",I35,I35/1000)</f>
+        <f t="shared" ref="K35:K66" si="8">IF(J35="T",I35,I35/1000)</f>
         <v>39</v>
       </c>
       <c r="L35" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2150</v>
       </c>
       <c r="M35" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>65302.325581395351</v>
       </c>
       <c r="N35" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43525</v>
       </c>
     </row>
-    <row r="36" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B36" s="14" t="s">
         <v>175</v>
       </c>
@@ -17016,31 +17059,31 @@
         <v>352</v>
       </c>
       <c r="I36" s="13">
-        <f>LEFT(D36,LEN(D36)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>37</v>
       </c>
       <c r="J36" s="13" t="str">
-        <f>LEFT(RIGHT(D36,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K36" s="13">
-        <f>IF(J36="T",I36,I36/1000)</f>
+        <f t="shared" si="8"/>
         <v>37</v>
       </c>
       <c r="L36" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2035</v>
       </c>
       <c r="M36" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>65454.545454545449</v>
       </c>
       <c r="N36" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43374</v>
       </c>
     </row>
-    <row r="37" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B37" s="14" t="s">
         <v>176</v>
       </c>
@@ -17063,31 +17106,31 @@
         <v>354</v>
       </c>
       <c r="I37" s="13">
-        <f>LEFT(D37,LEN(D37)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>37</v>
       </c>
       <c r="J37" s="13" t="str">
-        <f>LEFT(RIGHT(D37,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K37" s="13">
-        <f>IF(J37="T",I37,I37/1000)</f>
+        <f t="shared" si="8"/>
         <v>37</v>
       </c>
       <c r="L37" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2380</v>
       </c>
       <c r="M37" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>55966.386554621851</v>
       </c>
       <c r="N37" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43709</v>
       </c>
     </row>
-    <row r="38" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B38" s="14" t="s">
         <v>174</v>
       </c>
@@ -17110,31 +17153,31 @@
         <v>349</v>
       </c>
       <c r="I38" s="13">
-        <f>LEFT(D38,LEN(D38)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>34</v>
       </c>
       <c r="J38" s="13" t="str">
-        <f>LEFT(RIGHT(D38,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K38" s="13">
-        <f>IF(J38="T",I38,I38/1000)</f>
+        <f t="shared" si="8"/>
         <v>34</v>
       </c>
       <c r="L38" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>5000</v>
       </c>
       <c r="M38" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>24480</v>
       </c>
       <c r="N38" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43101</v>
       </c>
     </row>
-    <row r="39" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B39" s="14" t="s">
         <v>172</v>
       </c>
@@ -17157,31 +17200,31 @@
         <v>344</v>
       </c>
       <c r="I39" s="13">
-        <f>LEFT(D39,LEN(D39)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>33</v>
       </c>
       <c r="J39" s="13" t="str">
-        <f>LEFT(RIGHT(D39,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K39" s="13">
-        <f>IF(J39="T",I39,I39/1000)</f>
+        <f t="shared" si="8"/>
         <v>33</v>
       </c>
       <c r="L39" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2145</v>
       </c>
       <c r="M39" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>55384.615384615383</v>
       </c>
       <c r="N39" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43344</v>
       </c>
     </row>
-    <row r="40" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B40" s="14" t="s">
         <v>173</v>
       </c>
@@ -17204,31 +17247,31 @@
         <v>346</v>
       </c>
       <c r="I40" s="13">
-        <f>LEFT(D40,LEN(D40)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>33</v>
       </c>
       <c r="J40" s="13" t="str">
-        <f>LEFT(RIGHT(D40,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K40" s="13">
-        <f>IF(J40="T",I40,I40/1000)</f>
+        <f t="shared" si="8"/>
         <v>33</v>
       </c>
       <c r="L40" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3417</v>
       </c>
       <c r="M40" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>34767.339771729588</v>
       </c>
       <c r="N40" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43405</v>
       </c>
     </row>
-    <row r="41" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B41" s="14" t="s">
         <v>171</v>
       </c>
@@ -17251,31 +17294,31 @@
         <v>341</v>
       </c>
       <c r="I41" s="13">
-        <f>LEFT(D41,LEN(D41)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>32</v>
       </c>
       <c r="J41" s="13" t="str">
-        <f>LEFT(RIGHT(D41,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K41" s="13">
-        <f>IF(J41="T",I41,I41/1000)</f>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
       <c r="L41" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2200</v>
       </c>
       <c r="M41" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>52363.63636363636</v>
       </c>
       <c r="N41" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43344</v>
       </c>
     </row>
-    <row r="42" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B42" s="14" t="s">
         <v>170</v>
       </c>
@@ -17298,31 +17341,31 @@
         <v>338</v>
       </c>
       <c r="I42" s="13">
-        <f>LEFT(D42,LEN(D42)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>31</v>
       </c>
       <c r="J42" s="13" t="str">
-        <f>LEFT(RIGHT(D42,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K42" s="13">
-        <f>IF(J42="T",I42,I42/1000)</f>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
       <c r="L42" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1860</v>
       </c>
       <c r="M42" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>60000</v>
       </c>
       <c r="N42" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43678</v>
       </c>
     </row>
-    <row r="43" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B43" s="14" t="s">
         <v>169</v>
       </c>
@@ -17345,31 +17388,31 @@
         <v>335</v>
       </c>
       <c r="I43" s="13">
-        <f>LEFT(D43,LEN(D43)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="J43" s="13" t="str">
-        <f>LEFT(RIGHT(D43,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K43" s="13">
-        <f>IF(J43="T",I43,I43/1000)</f>
+        <f t="shared" si="8"/>
         <v>30</v>
       </c>
       <c r="L43" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1950</v>
       </c>
       <c r="M43" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>55384.615384615383</v>
       </c>
       <c r="N43" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43374</v>
       </c>
     </row>
-    <row r="44" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B44" s="14" t="s">
         <v>168</v>
       </c>
@@ -17392,31 +17435,31 @@
         <v>296</v>
       </c>
       <c r="I44" s="13">
-        <f>LEFT(D44,LEN(D44)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>28</v>
       </c>
       <c r="J44" s="13" t="str">
-        <f>LEFT(RIGHT(D44,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K44" s="13">
-        <f>IF(J44="T",I44,I44/1000)</f>
+        <f t="shared" si="8"/>
         <v>28</v>
       </c>
       <c r="L44" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2100</v>
       </c>
       <c r="M44" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>48000</v>
       </c>
       <c r="N44" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43435</v>
       </c>
     </row>
-    <row r="45" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B45" s="14" t="s">
         <v>167</v>
       </c>
@@ -17439,31 +17482,31 @@
         <v>332</v>
       </c>
       <c r="I45" s="13">
-        <f>LEFT(D45,LEN(D45)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>24.5</v>
       </c>
       <c r="J45" s="13" t="str">
-        <f>LEFT(RIGHT(D45,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K45" s="13">
-        <f>IF(J45="T",I45,I45/1000)</f>
+        <f t="shared" si="8"/>
         <v>24.5</v>
       </c>
       <c r="L45" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2100</v>
       </c>
       <c r="M45" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>42000</v>
       </c>
       <c r="N45" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43313</v>
       </c>
     </row>
-    <row r="46" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B46" s="14" t="s">
         <v>165</v>
       </c>
@@ -17486,31 +17529,31 @@
         <v>312</v>
       </c>
       <c r="I46" s="13">
-        <f>LEFT(D46,LEN(D46)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>24</v>
       </c>
       <c r="J46" s="13" t="str">
-        <f>LEFT(RIGHT(D46,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K46" s="13">
-        <f>IF(J46="T",I46,I46/1000)</f>
+        <f t="shared" si="8"/>
         <v>24</v>
       </c>
       <c r="L46" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1950</v>
       </c>
       <c r="M46" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>44307.692307692312</v>
       </c>
       <c r="N46" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43374</v>
       </c>
     </row>
-    <row r="47" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B47" s="14" t="s">
         <v>166</v>
       </c>
@@ -17533,31 +17576,31 @@
         <v>329</v>
       </c>
       <c r="I47" s="13">
-        <f>LEFT(D47,LEN(D47)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>24</v>
       </c>
       <c r="J47" s="13" t="str">
-        <f>LEFT(RIGHT(D47,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K47" s="13">
-        <f>IF(J47="T",I47,I47/1000)</f>
+        <f t="shared" si="8"/>
         <v>24</v>
       </c>
       <c r="L47" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1980</v>
       </c>
       <c r="M47" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>43636.36363636364</v>
       </c>
       <c r="N47" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43313</v>
       </c>
     </row>
-    <row r="48" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B48" s="14" t="s">
         <v>164</v>
       </c>
@@ -17580,31 +17623,31 @@
         <v>325</v>
       </c>
       <c r="I48" s="13">
-        <f>LEFT(D48,LEN(D48)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>22</v>
       </c>
       <c r="J48" s="13" t="str">
-        <f>LEFT(RIGHT(D48,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K48" s="13">
-        <f>IF(J48="T",I48,I48/1000)</f>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="L48" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1700</v>
       </c>
       <c r="M48" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>46588.23529411765</v>
       </c>
       <c r="N48" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43435</v>
       </c>
     </row>
-    <row r="49" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B49" s="14" t="s">
         <v>163</v>
       </c>
@@ -17627,31 +17670,31 @@
         <v>302</v>
       </c>
       <c r="I49" s="13">
-        <f>LEFT(D49,LEN(D49)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>20.5</v>
       </c>
       <c r="J49" s="13" t="str">
-        <f>LEFT(RIGHT(D49,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K49" s="13">
-        <f>IF(J49="T",I49,I49/1000)</f>
+        <f t="shared" si="8"/>
         <v>20.5</v>
       </c>
       <c r="L49" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1530</v>
       </c>
       <c r="M49" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>48235.294117647056</v>
       </c>
       <c r="N49" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43405</v>
       </c>
     </row>
-    <row r="50" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B50" s="14" t="s">
         <v>162</v>
       </c>
@@ -17674,31 +17717,31 @@
         <v>321</v>
       </c>
       <c r="I50" s="13">
-        <f>LEFT(D50,LEN(D50)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="J50" s="13" t="str">
-        <f>LEFT(RIGHT(D50,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K50" s="13">
-        <f>IF(J50="T",I50,I50/1000)</f>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="L50" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1700</v>
       </c>
       <c r="M50" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>42352.941176470587</v>
       </c>
       <c r="N50" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43344</v>
       </c>
     </row>
-    <row r="51" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B51" s="14" t="s">
         <v>160</v>
       </c>
@@ -17721,31 +17764,31 @@
         <v>315</v>
       </c>
       <c r="I51" s="13">
-        <f>LEFT(D51,LEN(D51)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="J51" s="13" t="str">
-        <f>LEFT(RIGHT(D51,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K51" s="13">
-        <f>IF(J51="T",I51,I51/1000)</f>
+        <f t="shared" si="8"/>
         <v>18</v>
       </c>
       <c r="L51" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1650</v>
       </c>
       <c r="M51" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>39272.727272727272</v>
       </c>
       <c r="N51" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43132</v>
       </c>
     </row>
-    <row r="52" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B52" s="14" t="s">
         <v>161</v>
       </c>
@@ -17768,31 +17811,31 @@
         <v>318</v>
       </c>
       <c r="I52" s="13">
-        <f>LEFT(D52,LEN(D52)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
       <c r="J52" s="13" t="str">
-        <f>LEFT(RIGHT(D52,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K52" s="13">
-        <f>IF(J52="T",I52,I52/1000)</f>
+        <f t="shared" si="8"/>
         <v>18</v>
       </c>
       <c r="L52" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1728</v>
       </c>
       <c r="M52" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>37500</v>
       </c>
       <c r="N52" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43313</v>
       </c>
     </row>
-    <row r="53" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B53" s="14" t="s">
         <v>159</v>
       </c>
@@ -17815,31 +17858,31 @@
         <v>312</v>
       </c>
       <c r="I53" s="13">
-        <f>LEFT(D53,LEN(D53)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>17.2</v>
       </c>
       <c r="J53" s="13" t="str">
-        <f>LEFT(RIGHT(D53,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K53" s="13">
-        <f>IF(J53="T",I53,I53/1000)</f>
+        <f t="shared" si="8"/>
         <v>17.2</v>
       </c>
       <c r="L53" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1570</v>
       </c>
       <c r="M53" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>39439.490445859868</v>
       </c>
       <c r="N53" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43221</v>
       </c>
     </row>
-    <row r="54" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B54" s="14" t="s">
         <v>154</v>
       </c>
@@ -17862,31 +17905,31 @@
         <v>302</v>
       </c>
       <c r="I54" s="13">
-        <f>LEFT(D54,LEN(D54)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="J54" s="13" t="str">
-        <f>LEFT(RIGHT(D54,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K54" s="13">
-        <f>IF(J54="T",I54,I54/1000)</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="L54" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1280</v>
       </c>
       <c r="M54" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>45000</v>
       </c>
       <c r="N54" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43647</v>
       </c>
     </row>
-    <row r="55" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B55" s="14" t="s">
         <v>155</v>
       </c>
@@ -17909,31 +17952,31 @@
         <v>304</v>
       </c>
       <c r="I55" s="13">
-        <f>LEFT(D55,LEN(D55)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="J55" s="13" t="str">
-        <f>LEFT(RIGHT(D55,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K55" s="13">
-        <f>IF(J55="T",I55,I55/1000)</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="L55" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1380</v>
       </c>
       <c r="M55" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>41739.130434782615</v>
       </c>
       <c r="N55" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43282</v>
       </c>
     </row>
-    <row r="56" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B56" s="14" t="s">
         <v>156</v>
       </c>
@@ -17956,31 +17999,31 @@
         <v>306</v>
       </c>
       <c r="I56" s="13">
-        <f>LEFT(D56,LEN(D56)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="J56" s="13" t="str">
-        <f>LEFT(RIGHT(D56,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K56" s="13">
-        <f>IF(J56="T",I56,I56/1000)</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="L56" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1400</v>
       </c>
       <c r="M56" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>41142.857142857145</v>
       </c>
       <c r="N56" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43282</v>
       </c>
     </row>
-    <row r="57" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B57" s="14" t="s">
         <v>157</v>
       </c>
@@ -18003,31 +18046,31 @@
         <v>298</v>
       </c>
       <c r="I57" s="13">
-        <f>LEFT(D57,LEN(D57)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="J57" s="13" t="str">
-        <f>LEFT(RIGHT(D57,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K57" s="13">
-        <f>IF(J57="T",I57,I57/1000)</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="L57" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1480</v>
       </c>
       <c r="M57" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>38918.91891891892</v>
       </c>
       <c r="N57" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43191</v>
       </c>
     </row>
-    <row r="58" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B58" s="14" t="s">
         <v>158</v>
       </c>
@@ -18050,31 +18093,31 @@
         <v>309</v>
       </c>
       <c r="I58" s="13">
-        <f>LEFT(D58,LEN(D58)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="J58" s="13" t="str">
-        <f>LEFT(RIGHT(D58,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K58" s="13">
-        <f>IF(J58="T",I58,I58/1000)</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="L58" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1760</v>
       </c>
       <c r="M58" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>32727.272727272728</v>
       </c>
       <c r="N58" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43221</v>
       </c>
     </row>
-    <row r="59" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B59" s="14" t="s">
         <v>153</v>
       </c>
@@ -18097,31 +18140,31 @@
         <v>296</v>
       </c>
       <c r="I59" s="13">
-        <f>LEFT(D59,LEN(D59)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>14.5</v>
       </c>
       <c r="J59" s="13" t="str">
-        <f>LEFT(RIGHT(D59,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K59" s="13">
-        <f>IF(J59="T",I59,I59/1000)</f>
+        <f t="shared" si="8"/>
         <v>14.5</v>
       </c>
       <c r="L59" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1350</v>
       </c>
       <c r="M59" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>38666.666666666664</v>
       </c>
       <c r="N59" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43313</v>
       </c>
     </row>
-    <row r="60" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B60" s="14" t="s">
         <v>150</v>
       </c>
@@ -18144,31 +18187,31 @@
         <v>296</v>
       </c>
       <c r="I60" s="13">
-        <f>LEFT(D60,LEN(D60)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>14</v>
       </c>
       <c r="J60" s="13" t="str">
-        <f>LEFT(RIGHT(D60,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K60" s="13">
-        <f>IF(J60="T",I60,I60/1000)</f>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="L60" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1320</v>
       </c>
       <c r="M60" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>38181.818181818177</v>
       </c>
       <c r="N60" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43221</v>
       </c>
     </row>
-    <row r="61" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B61" s="14" t="s">
         <v>151</v>
       </c>
@@ -18191,31 +18234,31 @@
         <v>298</v>
       </c>
       <c r="I61" s="13">
-        <f>LEFT(D61,LEN(D61)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>14</v>
       </c>
       <c r="J61" s="13" t="str">
-        <f>LEFT(RIGHT(D61,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K61" s="13">
-        <f>IF(J61="T",I61,I61/1000)</f>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="L61" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1372</v>
       </c>
       <c r="M61" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>36734.693877551021</v>
       </c>
       <c r="N61" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43040</v>
       </c>
     </row>
-    <row r="62" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B62" s="14" t="s">
         <v>149</v>
       </c>
@@ -18238,31 +18281,31 @@
         <v>294</v>
       </c>
       <c r="I62" s="13">
-        <f>LEFT(D62,LEN(D62)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>13.6</v>
       </c>
       <c r="J62" s="13" t="str">
-        <f>LEFT(RIGHT(D62,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K62" s="13">
-        <f>IF(J62="T",I62,I62/1000)</f>
+        <f t="shared" si="8"/>
         <v>13.6</v>
       </c>
       <c r="L62" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1290</v>
       </c>
       <c r="M62" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>37953.488372093023</v>
       </c>
       <c r="N62" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43191</v>
       </c>
     </row>
-    <row r="63" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B63" s="14" t="s">
         <v>145</v>
       </c>
@@ -18285,31 +18328,31 @@
         <v>264</v>
       </c>
       <c r="I63" s="13">
-        <f>LEFT(D63,LEN(D63)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>13.5</v>
       </c>
       <c r="J63" s="13" t="str">
-        <f>LEFT(RIGHT(D63,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K63" s="13">
-        <f>IF(J63="T",I63,I63/1000)</f>
+        <f t="shared" si="8"/>
         <v>13.5</v>
       </c>
       <c r="L63" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1310</v>
       </c>
       <c r="M63" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>37099.236641221374</v>
       </c>
       <c r="N63" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43678</v>
       </c>
     </row>
-    <row r="64" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B64" s="14" t="s">
         <v>147</v>
       </c>
@@ -18332,31 +18375,31 @@
         <v>288</v>
       </c>
       <c r="I64" s="13">
-        <f>LEFT(D64,LEN(D64)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>13.5</v>
       </c>
       <c r="J64" s="13" t="str">
-        <f>LEFT(RIGHT(D64,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K64" s="13">
-        <f>IF(J64="T",I64,I64/1000)</f>
+        <f t="shared" si="8"/>
         <v>13.5</v>
       </c>
       <c r="L64" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1323</v>
       </c>
       <c r="M64" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>36734.693877551021</v>
       </c>
       <c r="N64" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>42979</v>
       </c>
     </row>
-    <row r="65" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B65" s="14" t="s">
         <v>148</v>
       </c>
@@ -18379,31 +18422,31 @@
         <v>291</v>
       </c>
       <c r="I65" s="13">
-        <f>LEFT(D65,LEN(D65)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>13.5</v>
       </c>
       <c r="J65" s="13" t="str">
-        <f>LEFT(RIGHT(D65,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K65" s="13">
-        <f>IF(J65="T",I65,I65/1000)</f>
+        <f t="shared" si="8"/>
         <v>13.5</v>
       </c>
       <c r="L65" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1420</v>
       </c>
       <c r="M65" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>34225.352112676061</v>
       </c>
       <c r="N65" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43282</v>
       </c>
     </row>
-    <row r="66" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B66" s="14" t="s">
         <v>142</v>
       </c>
@@ -18426,31 +18469,31 @@
         <v>283</v>
       </c>
       <c r="I66" s="13">
-        <f>LEFT(D66,LEN(D66)-4)+0</f>
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="J66" s="13" t="str">
-        <f>LEFT(RIGHT(D66,4),1)</f>
+        <f t="shared" si="7"/>
         <v>T</v>
       </c>
       <c r="K66" s="13">
-        <f>IF(J66="T",I66,I66/1000)</f>
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="L66" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1280</v>
       </c>
       <c r="M66" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>36562.5</v>
       </c>
       <c r="N66" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>43221</v>
       </c>
     </row>
-    <row r="67" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B67" s="14" t="s">
         <v>143</v>
       </c>
@@ -18473,31 +18516,31 @@
         <v>284</v>
       </c>
       <c r="I67" s="13">
-        <f>LEFT(D67,LEN(D67)-4)+0</f>
+        <f t="shared" ref="I67:I85" si="9">LEFT(D67,LEN(D67)-4)+0</f>
         <v>13</v>
       </c>
       <c r="J67" s="13" t="str">
-        <f>LEFT(RIGHT(D67,4),1)</f>
+        <f t="shared" ref="J67:J85" si="10">LEFT(RIGHT(D67,4),1)</f>
         <v>T</v>
       </c>
       <c r="K67" s="13">
-        <f>IF(J67="T",I67,I67/1000)</f>
+        <f t="shared" ref="K67:K98" si="11">IF(J67="T",I67,I67/1000)</f>
         <v>13</v>
       </c>
       <c r="L67" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>1300</v>
       </c>
       <c r="M67" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>36000</v>
       </c>
       <c r="N67" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>42917</v>
       </c>
     </row>
-    <row r="68" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B68" s="14" t="s">
         <v>138</v>
       </c>
@@ -18520,31 +18563,31 @@
         <v>247</v>
       </c>
       <c r="I68" s="13">
-        <f>LEFT(D68,LEN(D68)-4)+0</f>
+        <f t="shared" si="9"/>
         <v>12.5</v>
       </c>
       <c r="J68" s="13" t="str">
-        <f>LEFT(RIGHT(D68,4),1)</f>
+        <f t="shared" si="10"/>
         <v>T</v>
       </c>
       <c r="K68" s="13">
-        <f>IF(J68="T",I68,I68/1000)</f>
+        <f t="shared" si="11"/>
         <v>12.5</v>
       </c>
       <c r="L68" s="13">
-        <f t="shared" ref="L68:L85" si="3">LEFT(E68,LEN(E68)-1)+0</f>
+        <f t="shared" ref="L68:L85" si="12">LEFT(E68,LEN(E68)-1)+0</f>
         <v>1225</v>
       </c>
       <c r="M68" s="11">
-        <f t="shared" ref="M68:M85" si="4">K68*60^2/(L68*1/1000)</f>
+        <f t="shared" ref="M68:M85" si="13">K68*60^2/(L68*1/1000)</f>
         <v>36734.693877551021</v>
       </c>
       <c r="N68" s="26">
-        <f t="shared" ref="N68:N85" si="5">DATE(RIGHT(C68,4)+0,MONTH(1&amp;LEFT(LEFT(C68,3),3)),1)</f>
+        <f t="shared" ref="N68:N85" si="14">DATE(RIGHT(C68,4)+0,MONTH(1&amp;LEFT(LEFT(C68,3),3)),1)</f>
         <v>42767</v>
       </c>
     </row>
-    <row r="69" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B69" s="14" t="s">
         <v>139</v>
       </c>
@@ -18567,31 +18610,31 @@
         <v>278</v>
       </c>
       <c r="I69" s="13">
-        <f>LEFT(D69,LEN(D69)-4)+0</f>
+        <f t="shared" si="9"/>
         <v>12.5</v>
       </c>
       <c r="J69" s="13" t="str">
-        <f>LEFT(RIGHT(D69,4),1)</f>
+        <f t="shared" si="10"/>
         <v>T</v>
       </c>
       <c r="K69" s="13">
-        <f>IF(J69="T",I69,I69/1000)</f>
+        <f t="shared" si="11"/>
         <v>12.5</v>
       </c>
       <c r="L69" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>1576</v>
       </c>
       <c r="M69" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>28553.299492385784</v>
       </c>
       <c r="N69" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>42948</v>
       </c>
     </row>
-    <row r="70" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B70" s="14" t="s">
         <v>141</v>
       </c>
@@ -18614,31 +18657,31 @@
         <v>280</v>
       </c>
       <c r="I70" s="13">
-        <f>LEFT(D70,LEN(D70)-4)+0</f>
+        <f t="shared" si="9"/>
         <v>12.5</v>
       </c>
       <c r="J70" s="13" t="str">
-        <f>LEFT(RIGHT(D70,4),1)</f>
+        <f t="shared" si="10"/>
         <v>T</v>
       </c>
       <c r="K70" s="13">
-        <f>IF(J70="T",I70,I70/1000)</f>
+        <f t="shared" si="11"/>
         <v>12.5</v>
       </c>
       <c r="L70" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>2050</v>
       </c>
       <c r="M70" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>21951.219512195123</v>
       </c>
       <c r="N70" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>43160</v>
       </c>
     </row>
-    <row r="71" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B71" s="14" t="s">
         <v>135</v>
       </c>
@@ -18661,31 +18704,31 @@
         <v>271</v>
       </c>
       <c r="I71" s="13">
-        <f>LEFT(D71,LEN(D71)-4)+0</f>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="J71" s="13" t="str">
-        <f>LEFT(RIGHT(D71,4),1)</f>
+        <f t="shared" si="10"/>
         <v>T</v>
       </c>
       <c r="K71" s="13">
-        <f>IF(J71="T",I71,I71/1000)</f>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="L71" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>1320</v>
       </c>
       <c r="M71" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>32727.272727272724</v>
       </c>
       <c r="N71" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>43221</v>
       </c>
     </row>
-    <row r="72" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B72" s="14" t="s">
         <v>137</v>
       </c>
@@ -18708,31 +18751,31 @@
         <v>274</v>
       </c>
       <c r="I72" s="13">
-        <f>LEFT(D72,LEN(D72)-4)+0</f>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="J72" s="13" t="str">
-        <f>LEFT(RIGHT(D72,4),1)</f>
+        <f t="shared" si="10"/>
         <v>T</v>
       </c>
       <c r="K72" s="13">
-        <f>IF(J72="T",I72,I72/1000)</f>
+        <f t="shared" si="11"/>
         <v>12</v>
       </c>
       <c r="L72" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>2000</v>
       </c>
       <c r="M72" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>21600</v>
       </c>
       <c r="N72" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>43101</v>
       </c>
     </row>
-    <row r="73" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B73" s="14" t="s">
         <v>131</v>
       </c>
@@ -18755,31 +18798,31 @@
         <v>262</v>
       </c>
       <c r="I73" s="13">
-        <f>LEFT(D73,LEN(D73)-4)+0</f>
+        <f t="shared" si="9"/>
         <v>11.5</v>
       </c>
       <c r="J73" s="13" t="str">
-        <f>LEFT(RIGHT(D73,4),1)</f>
+        <f t="shared" si="10"/>
         <v>T</v>
       </c>
       <c r="K73" s="13">
-        <f>IF(J73="T",I73,I73/1000)</f>
+        <f t="shared" si="11"/>
         <v>11.5</v>
       </c>
       <c r="L73" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>1127</v>
       </c>
       <c r="M73" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>36734.693877551021</v>
       </c>
       <c r="N73" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>42522</v>
       </c>
     </row>
-    <row r="74" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B74" s="14" t="s">
         <v>132</v>
       </c>
@@ -18802,31 +18845,31 @@
         <v>264</v>
       </c>
       <c r="I74" s="13">
-        <f>LEFT(D74,LEN(D74)-4)+0</f>
+        <f t="shared" si="9"/>
         <v>11.5</v>
       </c>
       <c r="J74" s="13" t="str">
-        <f>LEFT(RIGHT(D74,4),1)</f>
+        <f t="shared" si="10"/>
         <v>T</v>
       </c>
       <c r="K74" s="13">
-        <f>IF(J74="T",I74,I74/1000)</f>
+        <f t="shared" si="11"/>
         <v>11.5</v>
       </c>
       <c r="L74" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>1200</v>
       </c>
       <c r="M74" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>34500</v>
       </c>
       <c r="N74" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>43132</v>
       </c>
     </row>
-    <row r="75" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B75" s="14" t="s">
         <v>134</v>
       </c>
@@ -18849,31 +18892,31 @@
         <v>267</v>
       </c>
       <c r="I75" s="13">
-        <f>LEFT(D75,LEN(D75)-4)+0</f>
+        <f t="shared" si="9"/>
         <v>11.5</v>
       </c>
       <c r="J75" s="13" t="str">
-        <f>LEFT(RIGHT(D75,4),1)</f>
+        <f t="shared" si="10"/>
         <v>T</v>
       </c>
       <c r="K75" s="13">
-        <f>IF(J75="T",I75,I75/1000)</f>
+        <f t="shared" si="11"/>
         <v>11.5</v>
       </c>
       <c r="L75" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>1450</v>
       </c>
       <c r="M75" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>28551.724137931036</v>
       </c>
       <c r="N75" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>42826</v>
       </c>
     </row>
-    <row r="76" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B76" s="14" t="s">
         <v>130</v>
       </c>
@@ -18896,31 +18939,31 @@
         <v>258</v>
       </c>
       <c r="I76" s="13">
-        <f>LEFT(D76,LEN(D76)-4)+0</f>
+        <f t="shared" si="9"/>
         <v>10.5</v>
       </c>
       <c r="J76" s="13" t="str">
-        <f>LEFT(RIGHT(D76,4),1)</f>
+        <f t="shared" si="10"/>
         <v>T</v>
       </c>
       <c r="K76" s="13">
-        <f>IF(J76="T",I76,I76/1000)</f>
+        <f t="shared" si="11"/>
         <v>10.5</v>
       </c>
       <c r="L76" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>1432</v>
       </c>
       <c r="M76" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>26396.648044692738</v>
       </c>
       <c r="N76" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>43101</v>
       </c>
     </row>
-    <row r="77" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B77" s="14" t="s">
         <v>129</v>
       </c>
@@ -18943,31 +18986,31 @@
         <v>255</v>
       </c>
       <c r="I77" s="13">
-        <f>LEFT(D77,LEN(D77)-4)+0</f>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
       <c r="J77" s="13" t="str">
-        <f>LEFT(RIGHT(D77,4),1)</f>
+        <f t="shared" si="10"/>
         <v>T</v>
       </c>
       <c r="K77" s="13">
-        <f>IF(J77="T",I77,I77/1000)</f>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
       <c r="L77" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>1300</v>
       </c>
       <c r="M77" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>24923.076923076922</v>
       </c>
       <c r="N77" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>43101</v>
       </c>
     </row>
-    <row r="78" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B78" s="14" t="s">
         <v>127</v>
       </c>
@@ -18990,31 +19033,31 @@
         <v>251</v>
       </c>
       <c r="I78" s="13">
-        <f>LEFT(D78,LEN(D78)-4)+0</f>
+        <f t="shared" si="9"/>
         <v>8.6999999999999993</v>
       </c>
       <c r="J78" s="13" t="str">
-        <f>LEFT(RIGHT(D78,4),1)</f>
+        <f t="shared" si="10"/>
         <v>T</v>
       </c>
       <c r="K78" s="13">
-        <f>IF(J78="T",I78,I78/1000)</f>
+        <f t="shared" si="11"/>
         <v>8.6999999999999993</v>
       </c>
       <c r="L78" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>845</v>
       </c>
       <c r="M78" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>37065.08875739645</v>
       </c>
       <c r="N78" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>42767</v>
       </c>
     </row>
-    <row r="79" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B79" s="14" t="s">
         <v>125</v>
       </c>
@@ -19037,31 +19080,31 @@
         <v>247</v>
       </c>
       <c r="I79" s="13">
-        <f>LEFT(D79,LEN(D79)-4)+0</f>
+        <f t="shared" si="9"/>
         <v>8.5</v>
       </c>
       <c r="J79" s="13" t="str">
-        <f>LEFT(RIGHT(D79,4),1)</f>
+        <f t="shared" si="10"/>
         <v>T</v>
       </c>
       <c r="K79" s="13">
-        <f>IF(J79="T",I79,I79/1000)</f>
+        <f t="shared" si="11"/>
         <v>8.5</v>
       </c>
       <c r="L79" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>1000</v>
       </c>
       <c r="M79" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>30600</v>
       </c>
       <c r="N79" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>42979</v>
       </c>
     </row>
-    <row r="80" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B80" s="14" t="s">
         <v>123</v>
       </c>
@@ -19084,31 +19127,31 @@
         <v>243</v>
       </c>
       <c r="I80" s="13">
-        <f>LEFT(D80,LEN(D80)-4)+0</f>
+        <f t="shared" si="9"/>
         <v>7.3</v>
       </c>
       <c r="J80" s="13" t="str">
-        <f>LEFT(RIGHT(D80,4),1)</f>
+        <f t="shared" si="10"/>
         <v>T</v>
       </c>
       <c r="K80" s="13">
-        <f>IF(J80="T",I80,I80/1000)</f>
+        <f t="shared" si="11"/>
         <v>7.3</v>
       </c>
       <c r="L80" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>1150</v>
       </c>
       <c r="M80" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>22852.17391304348</v>
       </c>
       <c r="N80" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>42826</v>
       </c>
     </row>
-    <row r="81" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B81" s="14" t="s">
         <v>121</v>
       </c>
@@ -19131,31 +19174,31 @@
         <v>240</v>
       </c>
       <c r="I81" s="13">
-        <f>LEFT(D81,LEN(D81)-4)+0</f>
+        <f t="shared" si="9"/>
         <v>4.7300000000000004</v>
       </c>
       <c r="J81" s="13" t="str">
-        <f>LEFT(RIGHT(D81,4),1)</f>
+        <f t="shared" si="10"/>
         <v>T</v>
       </c>
       <c r="K81" s="13">
-        <f>IF(J81="T",I81,I81/1000)</f>
+        <f t="shared" si="11"/>
         <v>4.7300000000000004</v>
       </c>
       <c r="L81" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>1293</v>
       </c>
       <c r="M81" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>13169.373549883991</v>
       </c>
       <c r="N81" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>42248</v>
       </c>
     </row>
-    <row r="82" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B82" s="14" t="s">
         <v>119</v>
       </c>
@@ -19178,31 +19221,31 @@
         <v>236</v>
       </c>
       <c r="I82" s="13">
-        <f>LEFT(D82,LEN(D82)-4)+0</f>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="J82" s="13" t="str">
-        <f>LEFT(RIGHT(D82,4),1)</f>
+        <f t="shared" si="10"/>
         <v>T</v>
       </c>
       <c r="K82" s="13">
-        <f>IF(J82="T",I82,I82/1000)</f>
+        <f t="shared" si="11"/>
         <v>4</v>
       </c>
       <c r="L82" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>1027</v>
       </c>
       <c r="M82" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>14021.421616358326</v>
       </c>
       <c r="N82" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>43160</v>
       </c>
     </row>
-    <row r="83" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B83" s="14" t="s">
         <v>117</v>
       </c>
@@ -19225,31 +19268,31 @@
         <v>232</v>
       </c>
       <c r="I83" s="13">
-        <f>LEFT(D83,LEN(D83)-4)+0</f>
+        <f t="shared" si="9"/>
         <v>2.7</v>
       </c>
       <c r="J83" s="13" t="str">
-        <f>LEFT(RIGHT(D83,4),1)</f>
+        <f t="shared" si="10"/>
         <v>T</v>
       </c>
       <c r="K83" s="13">
-        <f>IF(J83="T",I83,I83/1000)</f>
+        <f t="shared" si="11"/>
         <v>2.7</v>
       </c>
       <c r="L83" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>697</v>
       </c>
       <c r="M83" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>13945.480631276901</v>
       </c>
       <c r="N83" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>42522</v>
       </c>
     </row>
-    <row r="84" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B84" s="14" t="s">
         <v>115</v>
       </c>
@@ -19272,31 +19315,31 @@
         <v>228</v>
       </c>
       <c r="I84" s="13">
-        <f>LEFT(D84,LEN(D84)-4)+0</f>
+        <f t="shared" si="9"/>
         <v>1.155</v>
       </c>
       <c r="J84" s="13" t="str">
-        <f>LEFT(RIGHT(D84,4),1)</f>
+        <f t="shared" si="10"/>
         <v>T</v>
       </c>
       <c r="K84" s="13">
-        <f>IF(J84="T",I84,I84/1000)</f>
+        <f t="shared" si="11"/>
         <v>1.155</v>
       </c>
       <c r="L84" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>590</v>
       </c>
       <c r="M84" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>7047.4576271186443</v>
       </c>
       <c r="N84" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>41974</v>
       </c>
     </row>
-    <row r="85" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:14" s="13" customFormat="1" ht="12" x14ac:dyDescent="0.25">
       <c r="B85" s="14" t="s">
         <v>112</v>
       </c>
@@ -19319,27 +19362,27 @@
         <v>224</v>
       </c>
       <c r="I85" s="13">
-        <f>LEFT(D85,LEN(D85)-4)+0</f>
+        <f t="shared" si="9"/>
         <v>478</v>
       </c>
       <c r="J85" s="13" t="str">
-        <f>LEFT(RIGHT(D85,4),1)</f>
+        <f t="shared" si="10"/>
         <v>G</v>
       </c>
       <c r="K85" s="13">
-        <f>IF(J85="T",I85,I85/1000)</f>
+        <f t="shared" si="11"/>
         <v>0.47799999999999998</v>
       </c>
       <c r="L85" s="13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>366</v>
       </c>
       <c r="M85" s="11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>4701.6393442622948</v>
       </c>
       <c r="N85" s="26">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>41821</v>
       </c>
     </row>
